--- a/tools/precos/planilhas/precos-oficiais-Anua.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Anua.xlsx
@@ -41,12 +41,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +588,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -635,7 +641,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,7 +696,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -745,7 +751,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -800,7 +806,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -853,7 +859,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -906,7 +912,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -959,7 +965,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1014,7 +1020,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1067,7 +1073,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1120,7 +1126,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1173,7 +1179,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1208,12 +1214,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003833</t>
+          <t>MB003869</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
+          <t>Collagen Retinol Refining Gua Sha Cream: creme para pescoço com retinol e aplicador 80 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1222,25 +1228,23 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>306.9</v>
+        <v>254.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Breakout Care Duo</t>
+          <t>Collagen Retinol Refining Gua Sha Cream</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1248,7 +1252,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/intensive-spot-care-duo</t>
+          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1263,12 +1267,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003869</t>
+          <t>MB002667</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Collagen Retinol Refining Gua Sha Cream: creme para pescoço com retinol e aplicador 80 ml</t>
+          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1277,23 +1281,25 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>254.9</v>
+        <v>481.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Collagen Retinol Refining Gua Sha Cream</t>
+          <t>Fall into Deep Hydration Set</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="I15" s="4" t="n"/>
+        <v>143</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1301,7 +1307,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
+          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1316,12 +1322,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB002667</t>
+          <t>MB003823</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
+          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1330,25 +1336,23 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>481.9</v>
+        <v>188.9</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set</t>
+          <t>Heartleaf 70 Daily Lotion</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>210</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1356,7 +1360,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
+          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1371,12 +1375,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003823</t>
+          <t>MB003809</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
+          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1389,12 +1393,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion</t>
+          <t>Heartleaf 70% Intense Calming Cream</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1409,7 +1413,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
+          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1424,12 +1428,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003809</t>
+          <t>MB002706</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1438,21 +1442,21 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>188.9</v>
+        <v>159.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" t="inlineStr">
@@ -1462,7 +1466,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
+          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1477,12 +1481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB002706</t>
+          <t>MB003832</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
+          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1491,16 +1495,16 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>159.9</v>
+        <v>160.9</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
+          <t>Heartleaf Centella Red Spot Cream</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1515,7 +1519,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
+          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1530,12 +1534,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003832</t>
+          <t>MB003813</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
+          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1544,16 +1548,16 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>160.9</v>
+        <v>159.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream</t>
+          <t>Heartleaf LHA Moisture Peeling Gel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1568,7 +1572,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
+          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1583,12 +1587,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003813</t>
+          <t>MB003811</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
+          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1601,12 +1605,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1636,12 +1640,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003821</t>
+          <t>MB003871</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
+          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1650,21 +1654,21 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>144.9</v>
+        <v>130.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Invisible Glow Finish Sunstick</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1689,12 +1693,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003811</t>
+          <t>MB003872</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
+          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1703,21 +1707,21 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>159.9</v>
+        <v>130.9</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Mineral Weightless Finish Sunscreen</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I23" s="4" t="n"/>
       <c r="J23" t="inlineStr">
@@ -1727,7 +1731,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1742,12 +1746,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003871</t>
+          <t>MB003835</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
+          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1756,21 +1760,21 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>130.9</v>
+        <v>166.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick</t>
+          <t>Niacinamide 5 TXA Brightening Pad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I24" s="4" t="n"/>
       <c r="J24" t="inlineStr">
@@ -1780,7 +1784,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
+          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1795,12 +1799,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003872</t>
+          <t>MB003859</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1809,21 +1813,21 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>130.9</v>
+        <v>152.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
@@ -1833,7 +1837,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1848,12 +1852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003814</t>
+          <t>MB003834</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1862,21 +1866,21 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>181.9</v>
+        <v>166.9</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1901,12 +1905,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB002695</t>
+          <t>MB003853</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
+          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1915,23 +1919,25 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>174.9</v>
+        <v>1821.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
+          <t>PDRN Glow Boost Full Routine Set</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" s="4" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>333.8</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1939,7 +1945,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -1954,12 +1960,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003835</t>
+          <t>MB002681</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1968,21 +1974,21 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>166.9</v>
+        <v>225.9</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" t="inlineStr">
@@ -1992,7 +1998,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2007,12 +2013,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003848</t>
+          <t>MB003862</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2021,21 +2027,21 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>152.9</v>
+        <v>108.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
@@ -2045,7 +2051,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2060,12 +2066,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003859</t>
+          <t>MB003861</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
+          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2074,21 +2080,21 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>152.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>PDRN Lip Serum</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
@@ -2098,7 +2104,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/pdrn-lip-serum</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2113,12 +2119,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003834</t>
+          <t>MB002675</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2127,21 +2133,25 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>166.9</v>
+        <v>663.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Basic Set</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="I31" s="4" t="n"/>
       <c r="J31" t="inlineStr">
@@ -2151,7 +2161,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2166,12 +2176,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003876</t>
+          <t>MB002674</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2180,21 +2190,25 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>210.9</v>
+        <v>765.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Basic Set</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" t="inlineStr">
@@ -2204,7 +2218,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2219,12 +2233,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003853</t>
+          <t>MB003810</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
+          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2233,25 +2247,23 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1821.9</v>
+        <v>159.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
+          <t>Peach 70% Niacinamide Serum</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>333.8</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I33" s="4" t="n"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2259,7 +2271,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2274,12 +2286,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB002681</t>
+          <t>MB003846</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
+          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2288,21 +2300,21 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>225.9</v>
+        <v>181.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
+          <t>Peach 77 Niacin Conditioning Milk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" t="inlineStr">
@@ -2312,7 +2324,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
+          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2327,12 +2339,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003862</t>
+          <t>MB003824</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
+          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2341,21 +2353,21 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>108.9</v>
+        <v>188.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>Peach 77 Niacin Enriched Cream</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
@@ -2365,7 +2377,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2380,12 +2392,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003861</t>
+          <t>MB003816</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
+          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2394,21 +2406,21 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>166.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum</t>
+          <t>Rice 70 Glow Milky Toner</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I36" s="4" t="n"/>
       <c r="J36" t="inlineStr">
@@ -2418,7 +2430,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-lip-serum</t>
+          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2433,12 +2445,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB002675</t>
+          <t>MB003831</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
+          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2447,25 +2459,21 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>663.9</v>
+        <v>144.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>Rice 70 Intensive Moisturizing Milk</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2475,7 +2483,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2490,12 +2498,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB002674</t>
+          <t>MB003819</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2504,25 +2512,21 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>765.9</v>
+        <v>166.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
@@ -2532,7 +2536,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2547,12 +2551,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003810</t>
+          <t>MB003818</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
+          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2561,21 +2565,21 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>159.9</v>
+        <v>144.9</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum</t>
+          <t>Rice Enzyme Brightening Cleansing Powder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
+          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2600,12 +2604,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003846</t>
+          <t>MB003829</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
+          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2614,21 +2618,21 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>181.9</v>
+        <v>123.9</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk</t>
+          <t>Ultra-Thin Spot Cover Patch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
@@ -2638,7 +2642,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
+          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2653,12 +2657,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003824</t>
+          <t>MB003864</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2667,21 +2671,21 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>188.9</v>
+        <v>131.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I41" s="4" t="n"/>
       <c r="J41" t="inlineStr">
@@ -2691,7 +2695,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
+          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2706,39 +2710,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003838</t>
+          <t>MB003808</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>582.9</v>
+        <v>166.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peach Brightening Set</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>85</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2746,7 +2748,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-brightening-set</t>
+          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2761,37 +2763,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003816</t>
+          <t>MB003858</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>166.9</v>
+        <v>502.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I43" s="4" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2799,7 +2807,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2814,35 +2822,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003831</t>
+          <t>MB003854</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
+          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>144.9</v>
+        <v>166.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk</t>
+          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
@@ -2852,7 +2860,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
+          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2867,35 +2875,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003819</t>
+          <t>MB003865</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>166.9</v>
+        <v>137.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
@@ -2905,7 +2913,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2920,35 +2928,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB003818</t>
+          <t>MB002726</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>144.9</v>
+        <v>137.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46" t="inlineStr">
@@ -2958,7 +2966,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -2973,12 +2981,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003856</t>
+          <t>MB003833</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
+          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2987,16 +2995,16 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+        <v>306.9</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo</t>
+          <t>Breakout Care Duo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3013,7 +3021,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/skin-recovery-duo</t>
+          <t>https://anua.us/products/intensive-spot-care-duo</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3028,12 +3036,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003829</t>
+          <t>MB003821</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
+          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3042,21 +3050,21 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
+        <v>144.9</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
@@ -3066,7 +3074,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3081,12 +3089,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003864</t>
+          <t>MB003814</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
+          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3095,21 +3103,21 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>131.9</v>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+        <v>181.9</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen</t>
+          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" t="inlineStr">
@@ -3119,7 +3127,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
+          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3134,35 +3142,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB003808</t>
+          <t>MB002695</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+        <v>174.9</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I50" s="4" t="n"/>
       <c r="J50" t="inlineStr">
@@ -3172,7 +3180,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
+          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3187,35 +3195,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003842</t>
+          <t>MB003848</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
+          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+        <v>152.9</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
@@ -3225,7 +3233,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3240,35 +3248,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003875</t>
+          <t>MB003876</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
+          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
+        <v>210.9</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+          <t>PDRN Collagen Glow Facial Serum Spray</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I52" s="4" t="n"/>
       <c r="J52" t="inlineStr">
@@ -3278,7 +3286,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3293,42 +3301,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003858</t>
+          <t>MB003838</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>502.9</v>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+        <v>582.9</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Full Care Set</t>
-        </is>
-      </c>
+          <t>Peach Brightening Set</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+          <t>https://anua.us/products/peach-brightening-set</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3352,38 +3356,38 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003868</t>
+          <t>MB003856</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
+          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1821.9</v>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
+        <v>305.9</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
+          <t>Skin Recovery Duo</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="4" t="n">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>333.8</v>
+        <v>50</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3392,7 +3396,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/skin-recovery-duo</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3407,12 +3411,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB003854</t>
+          <t>MB003842</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
+          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3421,21 +3425,21 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
+        <v>108.9</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I55" s="4" t="n"/>
       <c r="J55" t="inlineStr">
@@ -3445,7 +3449,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3460,12 +3464,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003865</t>
+          <t>MB003875</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3474,21 +3478,21 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
+        <v>144.9</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
@@ -3498,7 +3502,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3513,12 +3517,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB002726</t>
+          <t>MB003868</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3527,23 +3531,25 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
+        <v>1821.9</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>PDRN Glow Boost Full Routine Set</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I57" s="4" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>333.8</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3551,7 +3557,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3582,7 +3588,7 @@
       <c r="D58" s="2" t="n">
         <v>152.9</v>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3635,7 +3641,7 @@
       <c r="D59" s="2" t="n">
         <v>144.9</v>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3688,7 +3694,7 @@
       <c r="D60" s="2" t="n">
         <v>144.9</v>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3741,7 +3747,7 @@
       <c r="D61" s="2" t="n">
         <v>159.9</v>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3794,7 +3800,7 @@
       <c r="D62" s="2" t="n">
         <v>159.9</v>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3847,7 +3853,7 @@
       <c r="D63" s="2" t="n">
         <v>152.9</v>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3900,7 +3906,7 @@
       <c r="D64" s="2" t="n">
         <v>437.9</v>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -3953,7 +3959,7 @@
       <c r="D65" s="2" t="n">
         <v>844.9</v>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -4008,7 +4014,7 @@
       <c r="D66" s="2" t="n">
         <v>159.9</v>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -4061,7 +4067,7 @@
       <c r="D67" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -4116,7 +4122,7 @@
       <c r="D68" s="2" t="n">
         <v>152.9</v>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -8737,7 +8743,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:03 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-Anua.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Anua.xlsx
@@ -165,8 +165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N82" headerRowCount="1">
-  <autoFilter ref="A1:N82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N163" headerRowCount="1">
+  <autoFilter ref="A1:N163"/>
   <tableColumns count="14">
     <tableColumn id="1" name="SKU"/>
     <tableColumn id="2" name="Nosso produto"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1108,12 +1108,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003847</t>
+          <t>MB002727</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer: hidratante calmante 3% 100 ml</t>
+          <t>Azelaic Acid 10 Hyaluron Redness Soothing Serum: sérum calmante 30 ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>137.9</v>
+        <v>174.9</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>Azelaic Acid 10 Hyaluron Redness Soothing Serum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/azelaic-acid-10-hyaluron-redness-soothing-serum-1</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1161,12 +1161,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003822</t>
+          <t>MB003847</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BHA 2% Gentle Exfoliating Toner: tônico esfoliante suave com ácido salicílico 150 ml</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer: hidratante calmante 3% 100 ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>144.9</v>
+        <v>137.9</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BHA 2% Gentle Exfoliating Toner</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/bha-2-gentle-exfoliating-toner</t>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1214,12 +1214,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003869</t>
+          <t>MB003822</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Collagen Retinol Refining Gua Sha Cream: creme para pescoço com retinol e aplicador 80 ml</t>
+          <t>BHA 2% Gentle Exfoliating Toner: tônico esfoliante suave com ácido salicílico 150 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>254.9</v>
+        <v>144.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Collagen Retinol Refining Gua Sha Cream</t>
+          <t>BHA 2% Gentle Exfoliating Toner</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
+          <t>https://anua.us/products/bha-2-gentle-exfoliating-toner</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1267,12 +1267,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB002667</t>
+          <t>MB002725</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
+          <t>Barrier Reboot Daily Moisturizer: hidratante diário de barreira 100 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>481.9</v>
+        <v>174.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1290,16 +1290,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set</t>
+          <t>Barrier Reboot Daily Moisturizer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>210</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1307,7 +1305,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
+          <t>https://anua.us/products/barrier-reboot-daily-moisturizer-1</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1322,12 +1320,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003823</t>
+          <t>MB002724</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
+          <t>Barrier Reboot Intensive Cream: creme intensivo de barreira para pele seca 100 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1345,7 +1343,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion</t>
+          <t>Barrier Reboot Intensive Cream</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1360,7 +1358,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
+          <t>https://anua.us/products/barrier-reboot-intensive-cream-1</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1375,12 +1373,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003809</t>
+          <t>MB002723</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
+          <t>Barrier Reboot Water Gel Cream: gel-creme de barreira para pele oleosa 100 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1398,7 +1396,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream</t>
+          <t>Barrier Reboot Water Gel Cream</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1413,7 +1411,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
+          <t>https://anua.us/products/barrier-reboot-water-gel-cream</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1428,12 +1426,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB002706</t>
+          <t>MB003869</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
+          <t>Collagen Retinol Refining Gua Sha Cream: creme para pescoço com retinol e aplicador 80 ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1442,7 +1440,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>159.9</v>
+        <v>254.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1451,12 +1449,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
+          <t>Collagen Retinol Refining Gua Sha Cream</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" t="inlineStr">
@@ -1466,7 +1464,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
+          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1481,12 +1479,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003832</t>
+          <t>MB002719</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
+          <t>Dark Spot Prep &amp; Boost Duo: discos TXA + sérum de niacinamida e TXA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1495,7 +1493,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>160.9</v>
+        <v>342.9</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1504,14 +1502,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream</t>
+          <t>Dark Spot Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I19" s="4" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
+          <t>https://anua.us/products/txa-pad-serum-duo</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1534,12 +1534,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003813</t>
+          <t>MB002716</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
+          <t>Even Tone &amp; Barrier Set: discos TXA + sérum de niacinamida + creme de ceramidas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>159.9</v>
+        <v>503.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1557,14 +1557,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel</t>
+          <t>Even Tone &amp; Barrier Set</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I20" s="4" t="n"/>
+        <v>62.5</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>73</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1572,7 +1574,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
+          <t>https://anua.us/products/even-tone-barrier-set</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1587,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003811</t>
+          <t>MB002715</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
+          <t>Even Tone &amp; Pore Refining Duo: tônico BHA 2% + sérum de niacinamida e TXA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1601,7 +1603,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>159.9</v>
+        <v>313.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1610,14 +1612,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Even tone &amp; Pore Refining Duo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I21" s="4" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>48</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/even-tone-pore-refining-duo</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1640,12 +1644,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003871</t>
+          <t>MB002666</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
+          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Complete Set</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1654,7 +1658,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>130.9</v>
+        <v>481.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1663,14 +1667,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick</t>
+          <t>Fall into Deep Hydration Set</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I22" s="4" t="n"/>
+        <v>143</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1678,7 +1684,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
+          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1693,12 +1699,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003872</t>
+          <t>MB002667</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
+          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1707,7 +1713,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>130.9</v>
+        <v>481.9</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -1716,14 +1722,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen</t>
+          <t>Fall into Deep Hydration Set</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="4" t="n"/>
+        <v>143</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1731,7 +1739,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
+          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1746,12 +1754,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003835</t>
+          <t>MB003823</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
+          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1760,7 +1768,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>166.9</v>
+        <v>188.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1769,12 +1777,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad</t>
+          <t>Heartleaf 70 Daily Lotion</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I24" s="4" t="n"/>
       <c r="J24" t="inlineStr">
@@ -1784,7 +1792,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
+          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1799,12 +1807,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003859</t>
+          <t>MB003809</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
+          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1813,7 +1821,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>152.9</v>
+        <v>188.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1822,12 +1830,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>Heartleaf 70% Intense Calming Cream</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1852,12 +1860,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003834</t>
+          <t>MB002709</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
+          <t>Heartleaf 77 Clear Pad: discos tônicos com heartleaf e PHA (70 unidades)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1875,7 +1883,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1890,7 +1898,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
+          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1905,12 +1913,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003853</t>
+          <t>MB002707</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
+          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 250ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1919,7 +1927,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1821.9</v>
+        <v>166.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1928,16 +1936,18 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Heartleaf 77 Soothing Toner</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>333.8</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1945,7 +1955,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356121366</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -1960,12 +1970,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB002681</t>
+          <t>MB002708</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
+          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 500ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1974,7 +1984,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>225.9</v>
+        <v>250.9</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1983,12 +1993,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Heartleaf 77 Soothing Toner</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="n">
-        <v>31</v>
+        <v>34.5</v>
       </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" t="inlineStr">
@@ -1998,7 +2012,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
+          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356154134</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2013,12 +2027,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003862</t>
+          <t>MB002706</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2027,7 +2041,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>108.9</v>
+        <v>159.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -2036,12 +2050,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
@@ -2051,7 +2065,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2066,12 +2080,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003861</t>
+          <t>MB003832</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
+          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2080,7 +2094,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>160.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -2089,12 +2103,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum</t>
+          <t>Heartleaf Centella Red Spot Cream</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
@@ -2104,7 +2118,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-lip-serum</t>
+          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2119,12 +2133,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB002675</t>
+          <t>MB003813</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
+          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2133,7 +2147,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>663.9</v>
+        <v>159.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -2142,16 +2156,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>Heartleaf LHA Moisture Peeling Gel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I31" s="4" t="n"/>
       <c r="J31" t="inlineStr">
@@ -2161,7 +2171,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2176,12 +2186,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB002674</t>
+          <t>MB003811</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
+          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2190,7 +2200,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>765.9</v>
+        <v>159.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -2199,16 +2209,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" s="4" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" t="inlineStr">
@@ -2218,7 +2224,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2233,12 +2239,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003810</t>
+          <t>MB003871</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
+          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2247,7 +2253,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>159.9</v>
+        <v>130.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -2256,12 +2262,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum</t>
+          <t>Invisible Glow Finish Sunstick</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I33" s="4" t="n"/>
       <c r="J33" t="inlineStr">
@@ -2271,7 +2277,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
+          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2286,12 +2292,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003846</t>
+          <t>MB002698</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
+          <t>Invisible Matte Finish Sunscreen: protetor solar matte FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2300,7 +2306,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>181.9</v>
+        <v>160.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -2309,12 +2315,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk</t>
+          <t>Invisible Matte Finish Sunscreen</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" t="inlineStr">
@@ -2324,7 +2330,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
+          <t>https://anua.us/products/invisible-matte-finish-sunscreen</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2339,12 +2345,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003824</t>
+          <t>MB003872</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
+          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2353,7 +2359,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>188.9</v>
+        <v>130.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -2362,12 +2368,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream</t>
+          <t>Mineral Weightless Finish Sunscreen</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
@@ -2377,7 +2383,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
+          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2392,12 +2398,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003816</t>
+          <t>MB003835</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
+          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2415,7 +2421,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner</t>
+          <t>Niacinamide 5 TXA Brightening Pad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2430,7 +2436,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
+          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2445,12 +2451,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003831</t>
+          <t>MB003859</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2459,7 +2465,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>144.9</v>
+        <v>152.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -2468,12 +2474,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2483,7 +2489,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2498,12 +2504,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003819</t>
+          <t>MB003834</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2521,7 +2527,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2536,7 +2542,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2551,12 +2557,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003818</t>
+          <t>MB002688</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini: bruma sérum de PDRN 30 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2574,7 +2580,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder</t>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2589,7 +2595,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
+          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2604,12 +2610,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003829</t>
+          <t>MB002684</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Full Care Set</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2618,7 +2624,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>123.9</v>
+        <v>742.9</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -2627,14 +2633,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I40" s="4" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2642,7 +2654,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2657,12 +2669,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003864</t>
+          <t>MB002685</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Trial Set</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2671,7 +2683,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>131.9</v>
+        <v>502.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -2680,14 +2692,20 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
       <c r="H41" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I41" s="4" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2695,7 +2713,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2710,21 +2728,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003808</t>
+          <t>MB002683</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo: discos de PDRN + sérum de PDRN 30 ml</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>166.9</v>
+        <v>350.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -2733,14 +2751,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I42" s="4" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2748,7 +2768,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
+          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2763,21 +2783,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003858</t>
+          <t>MB003853</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>502.9</v>
+        <v>1821.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -2786,19 +2806,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Full Care Set</t>
-        </is>
-      </c>
+          <t>PDRN Glow Boost Full Routine Set</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" s="4" t="n">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>124</v>
+        <v>333.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2807,7 +2823,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2822,21 +2838,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003854</t>
+          <t>MB002681</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>166.9</v>
+        <v>225.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2845,12 +2861,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
@@ -2860,7 +2876,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2875,21 +2891,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003865</t>
+          <t>MB002680</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum: sérum de PDRN com cápsulas</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>137.9</v>
+        <v>181.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -2898,12 +2914,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
@@ -2913,7 +2929,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-one-day-serum</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2928,21 +2944,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB002726</t>
+          <t>MB002678</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask: máscara de PDRN (2 caixas de 10)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>137.9</v>
+        <v>209.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -2951,14 +2967,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I46" s="4" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>57.6</v>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2966,7 +2984,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-mask</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -2981,12 +2999,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003833</t>
+          <t>MB003862</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2995,25 +3013,23 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>306.9</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>108.9</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Breakout Care Duo</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3021,7 +3037,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/intensive-spot-care-duo</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3036,12 +3052,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003821</t>
+          <t>MB003861</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
+          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3050,21 +3066,21 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>PDRN Lip Serum</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
@@ -3074,7 +3090,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/pdrn-lip-serum</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3089,12 +3105,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003814</t>
+          <t>MB002675</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3103,21 +3119,25 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>663.9</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Basic Set</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" t="inlineStr">
@@ -3127,7 +3147,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3142,12 +3162,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB002695</t>
+          <t>MB002674</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3156,21 +3176,25 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>765.9</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Basic Set</t>
+        </is>
+      </c>
       <c r="H50" s="4" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="I50" s="4" t="n"/>
       <c r="J50" t="inlineStr">
@@ -3180,7 +3204,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3195,12 +3219,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003848</t>
+          <t>MB003810</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
+          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3209,21 +3233,21 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>159.9</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
+          <t>Peach 70% Niacinamide Serum</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
@@ -3233,7 +3257,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
+          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3248,12 +3272,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003876</t>
+          <t>MB003846</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
+          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3262,21 +3286,21 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>210.9</v>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray</t>
+          <t>Peach 77 Niacin Conditioning Milk</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I52" s="4" t="n"/>
       <c r="J52" t="inlineStr">
@@ -3286,7 +3310,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3301,12 +3325,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003838</t>
+          <t>MB003824</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
+          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3315,25 +3339,23 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>582.9</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>188.9</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Peach Brightening Set</t>
+          <t>Peach 77 Niacin Enriched Cream</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I53" s="4" t="n"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3341,7 +3363,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-brightening-set</t>
+          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3356,12 +3378,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003856</t>
+          <t>MB002669</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
+          <t>Peach 77 Niacin Essence Toner: tônico essência de pêssego 250 ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3370,25 +3392,23 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo</t>
+          <t>Peach 77 Niacin Essence Toner</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I54" s="4" t="n"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3396,7 +3416,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/skin-recovery-duo</t>
+          <t>https://anua.us/products/peach-77-niacin-essence-toner-1</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3411,37 +3431,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB003842</t>
+          <t>MB002664</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
+          <t>Redness Soothing Prep &amp; Boost Duo: discos + sérum de ácido azelaico</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>327.9</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>Redness Soothing Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I55" s="4" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3449,7 +3471,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/azelaic-pad-serum-duo</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3464,35 +3486,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003875</t>
+          <t>MB002663</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
+          <t>Retinol 0,1 Caffeine Revitalizing Eye Cream: creme para os olhos 30 ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>166.9</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
@@ -3502,7 +3524,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
+          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3517,38 +3539,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB003868</t>
+          <t>MB002662</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
+          <t>Retinol Anti-Aging Duo: sérum de retinol 0,3% + creme de olhos com retinol</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1821.9</v>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>320.9</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
+          <t>Retinol Anti-Aging Duo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="4" t="n">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>333.8</v>
+        <v>47</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3557,7 +3579,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/retinol-anti-aging-duo</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3572,12 +3594,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003843</t>
+          <t>MB003816</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Golden Honmoon Ceramide Barrier Collagen Mask: máscara de colágeno (4 un.)</t>
+          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3586,21 +3608,21 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>166.9</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+          <t>Rice 70 Glow Milky Toner</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I58" s="4" t="n"/>
       <c r="J58" t="inlineStr">
@@ -3610,7 +3632,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3625,12 +3647,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB002687</t>
+          <t>MB003831</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Glass Skin: adesivo de colágeno para o rosto (4 un.)</t>
+          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3641,14 +3663,14 @@
       <c r="D59" s="2" t="n">
         <v>144.9</v>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Glass Skin 4ea</t>
+          <t>Rice 70 Intensive Moisturizing Milk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3663,7 +3685,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-glass-skin-4ea-1</t>
+          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3678,12 +3700,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB003844</t>
+          <t>MB003819</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Neck: adesivo de colágeno para o pescoço (4 un.)</t>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3692,21 +3714,21 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>166.9</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Neck 4ea</t>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I60" s="4" t="n"/>
       <c r="J60" t="inlineStr">
@@ -3716,7 +3738,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-neck-4ea-1</t>
+          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3731,12 +3753,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003825</t>
+          <t>MB003818</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Peach 70 Niacin Brightening Collagen Mask: máscara iluminadora de colágeno (4 un.)</t>
+          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3745,21 +3767,21 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>144.9</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Peach 70 Niacin Brightening Collagen Mask</t>
+          <t>Rice Enzyme Brightening Cleansing Powder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I61" s="4" t="n"/>
       <c r="J61" t="inlineStr">
@@ -3769,7 +3791,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacin-brightening-collagen-mask-1</t>
+          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3784,12 +3806,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB003827</t>
+          <t>MB002656</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Collagen Mask: máscara de colágeno com arroz (4 unidades)</t>
+          <t>Rice Nourishing Full Set: rotina de arroz em 5 passos para pele seca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3798,23 +3820,25 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>680.9</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Collagen Mask</t>
+          <t>Rice Nourishing Full Set for Dry Skin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I62" s="4" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>108</v>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3822,7 +3846,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
+          <t>https://anua.us/products/rice-glow-full-set</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3837,35 +3861,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003863</t>
+          <t>MB002655</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
+          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas (55 unidades)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>102.9</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+          <t>Rumi Ultra-thin Spot Cover Patch (55ea)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I63" s="4" t="n"/>
       <c r="J63" t="inlineStr">
@@ -3875,7 +3899,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-55ea</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3890,35 +3914,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB004044</t>
+          <t>MB002654</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml (kit com 2)</t>
+          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas com estojo (28 un.)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>102.9</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
+          <t>Rumi Ultra-thin Spot Cover Patch with Case (28ea)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I64" s="4" t="n"/>
       <c r="J64" t="inlineStr">
@@ -3928,7 +3952,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
+          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-with-case-28ea</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -3943,12 +3967,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB003855</t>
+          <t>MB002651</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7-Day Ultimate Glass Glow Set: rotina glass skin em 7 passos</t>
+          <t>Triple Acid Spot Care Microdart Patch: adesivo localizado com microdarts (12 un.)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3957,25 +3981,23 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>844.9</v>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>108.9</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>7-Day Glass Skin Set</t>
+          <t>Triple Acid Spot Care Microdart Patch</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>165</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I65" s="4" t="n"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3983,7 +4005,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/7-day-glass-skin-set</t>
+          <t>https://anua.us/products/triple-acid-spot-care-microdart-patch-1</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -3998,12 +4020,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB003817</t>
+          <t>MB003829</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Heartleaf Low pH Deep Cleansing Water: água de limpeza de pH baixo</t>
+          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4012,21 +4034,21 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>123.9</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
+          <t>Ultra-Thin Spot Cover Patch</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I66" s="4" t="n"/>
       <c r="J66" t="inlineStr">
@@ -4036,7 +4058,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
+          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4051,38 +4073,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB003870</t>
+          <t>MB002649</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Duo Essencial Diário PDRN</t>
+          <t>Youthful Glow Set for over 30+: rotina de 5 passos com PDRN e retinol</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>742.9</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
+          <t>Youthful Glow Set for over 30+</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4091,7 +4113,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
+          <t>https://anua.us/products/black-friday-exclusive-set-special-gift-30-sheet-masks</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4106,35 +4128,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003841</t>
+          <t>MB003864</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tônico Booster PDRN 100 com Ácido Hialurônico</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>131.9</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I68" s="4" t="n"/>
       <c r="J68" t="inlineStr">
@@ -4144,7 +4166,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4159,12 +4181,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003857</t>
+          <t>MB003808</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adesivo Derretível de Colágeno PDRN para Pescoço (4 unidades)</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4173,27 +4195,51 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="n"/>
+        <v>166.9</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Heartleaf 77 Clear Pad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="I69" s="4" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="6" t="n"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
+        </is>
+      </c>
+      <c r="L69" s="2">
+        <f>ROUND(H69*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M69" s="6">
+        <f>IF(OR(D69="",L69=""),"",D69/L69-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB003994</t>
+          <t>MB002701</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anua Kit de Patches Firmadores Melting com Colágeno PDRN</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4202,27 +4248,51 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="4" t="n">
+        <v>22</v>
+      </c>
       <c r="I70" s="4" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="6" t="n"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+        </is>
+      </c>
+      <c r="L70" s="2">
+        <f>ROUND(H70*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M70" s="6">
+        <f>IF(OR(D70="",L70=""),"",D70/L70-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB003812</t>
+          <t>MB002648</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Espuma de Limpeza Profunda para Poros com Heartleaf e Quercetinol</t>
+          <t>Moisturizing Finish Zero-cast Sunscreen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4231,27 +4301,51 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="n"/>
+        <v>130.9</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Zero-cast Moisturizing Finish Sunscreen</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I71" s="4" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="6" t="n"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
+        </is>
+      </c>
+      <c r="L71" s="2">
+        <f>ROUND(H71*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M71" s="6">
+        <f>IF(OR(D71="",L71=""),"",D71/L71-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003839</t>
+          <t>MB003858</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kit Completo Nutritivo de Arroz para Pele Seca</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4260,27 +4354,57 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>680.9</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="6" t="n"/>
+        <v>502.9</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+        </is>
+      </c>
+      <c r="L72" s="2">
+        <f>ROUND(H72*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M72" s="6">
+        <f>IF(OR(D72="",L72=""),"",D72/L72-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003860</t>
+          <t>MB003854</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kit PDRN Glowy Skin 4 Passos</t>
+          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4289,27 +4413,51 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>874.9</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n"/>
+        <v>166.9</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="I73" s="4" t="n"/>
-      <c r="L73" s="2" t="n"/>
-      <c r="M73" s="6" t="n"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
+        </is>
+      </c>
+      <c r="L73" s="2">
+        <f>ROUND(H73*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M73" s="6">
+        <f>IF(OR(D73="",L73=""),"",D73/L73-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003873</t>
+          <t>MB002726</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kit PDRN Luminosidade Radiante o Dia Todo</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4318,27 +4466,51 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="n"/>
+        <v>137.9</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I74" s="4" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="6" t="n"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+        </is>
+      </c>
+      <c r="L74" s="2">
+        <f>ROUND(H74*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M74" s="6">
+        <f>IF(OR(D74="",L74=""),"",D74/L74-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB002735</t>
+          <t>MB003865</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kit Rotina 7 Dias Manchas Escuras</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4347,220 +4519,3823 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1012.9</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n"/>
+        <v>137.9</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I75" s="4" t="n"/>
-      <c r="L75" s="2" t="n"/>
-      <c r="M75" s="6" t="n"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+        </is>
+      </c>
+      <c r="L75" s="2">
+        <f>ROUND(H75*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M75" s="6">
+        <f>IF(OR(D75="",L75=""),"",D75/L75-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB003866</t>
+          <t>MB002737</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Leite Condicionador de Pêssego 77 Niacina</t>
+          <t>5-step Korean Skincare Set: rotina coreana de 5 passos Heartleaf + TXA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
-      <c r="L76" s="2" t="n"/>
-      <c r="M76" s="6" t="n"/>
+        <v>706.9</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>5-step Korean Skincare Set</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="4" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/glass-skin-full-routine-set</t>
+        </is>
+      </c>
+      <c r="L76" s="2">
+        <f>ROUND(H76*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M76" s="6">
+        <f>IF(OR(D76="",L76=""),"",D76/L76-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003826</t>
+          <t>MB003833</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Calmante com Houttuynia Cordata 70</t>
+          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="6" t="n"/>
+        <v>306.9</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Breakout Care Duo</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/intensive-spot-care-duo</t>
+        </is>
+      </c>
+      <c r="L77" s="2">
+        <f>ROUND(H77*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M77" s="6">
+        <f>IF(OR(D77="",L77=""),"",D77/L77-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB003830</t>
+          <t>MB002717</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Patch Microagulhado para Tratamento de Espinhas com Tríplice Ácido</t>
+          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 1 Set</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="6" t="n"/>
+        <v>437.9</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Double Cleansing Duo Set of 2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+        </is>
+      </c>
+      <c r="L78" s="2">
+        <f>ROUND(H78*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M78" s="6">
+        <f>IF(OR(D78="",L78=""),"",D78/L78-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB003840</t>
+          <t>MB002718</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sérum PDRN Cápsula 100 de Ácido Hialurônico – Dose Única</t>
+          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 2 Sets(+Gifts)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
-      <c r="L79" s="2" t="n"/>
-      <c r="M79" s="6" t="n"/>
+        <v>437.9</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Double Cleansing Duo Set of 2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+        </is>
+      </c>
+      <c r="L79" s="2">
+        <f>ROUND(H79*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M79" s="6">
+        <f>IF(OR(D79="",L79=""),"",D79/L79-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB003867</t>
+          <t>MB002714</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tônico Booster Iluminador com Niacinamida e Ácido Tranexâmico</t>
+          <t>Glass Skin Essential Set: limpeza dupla Heartleaf + sérum de niacinamida e TXA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="6" t="n"/>
+        <v>844.9</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Glass Skin Essential Set</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/glass-skin-essential-set</t>
+        </is>
+      </c>
+      <c r="L80" s="2">
+        <f>ROUND(H80*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M80" s="6">
+        <f>IF(OR(D80="",L80=""),"",D80/L80-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003845</t>
+          <t>MB002705</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tônico Essência de Pêssego 77 com Niacinamida</t>
+          <t>Heartleaf Centella Redness Cream</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n"/>
+        <v>159.9</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Heartleaf Centella Red Spot Cream</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="4" t="n">
+        <v>22</v>
+      </c>
       <c r="I81" s="4" t="n"/>
-      <c r="L81" s="2" t="n"/>
-      <c r="M81" s="6" t="n"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
+        </is>
+      </c>
+      <c r="L81" s="2">
+        <f>ROUND(H81*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M81" s="6">
+        <f>IF(OR(D81="",L81=""),"",D81/L81-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>MB003821</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+        </is>
+      </c>
+      <c r="L82" s="2">
+        <f>ROUND(H82*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M82" s="6">
+        <f>IF(OR(D82="",L82=""),"",D82/L82-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MB002700</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Heartleaf Quercetinol: espuma de limpeza profunda para os poros 150 ml</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
+        </is>
+      </c>
+      <c r="L83" s="2">
+        <f>ROUND(H83*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M83" s="6">
+        <f>IF(OR(D83="",L83=""),"",D83/L83-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MB002697</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Light Finish Mineral Sunscreen</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mineral Weightless Finish Sunscreen</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I84" s="4" t="n"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
+        </is>
+      </c>
+      <c r="L84" s="2">
+        <f>ROUND(H84*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M84" s="6">
+        <f>IF(OR(D84="",L84=""),"",D84/L84-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MB003814</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+        </is>
+      </c>
+      <c r="L85" s="2">
+        <f>ROUND(H85*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M85" s="6">
+        <f>IF(OR(D85="",L85=""),"",D85/L85-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MB002695</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I86" s="4" t="n"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
+        </is>
+      </c>
+      <c r="L86" s="2">
+        <f>ROUND(H86*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M86" s="6">
+        <f>IF(OR(D86="",L86=""),"",D86/L86-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MB003848</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
+        </is>
+      </c>
+      <c r="L87" s="2">
+        <f>ROUND(H87*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M87" s="6">
+        <f>IF(OR(D87="",L87=""),"",D87/L87-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MB003876</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Glow Facial Serum Spray</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I88" s="4" t="n"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+        </is>
+      </c>
+      <c r="L88" s="2">
+        <f>ROUND(H88*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M88" s="6">
+        <f>IF(OR(D88="",L88=""),"",D88/L88-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MB002679</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
+        </is>
+      </c>
+      <c r="L89" s="2">
+        <f>ROUND(H89*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M89" s="6">
+        <f>IF(OR(D89="",L89=""),"",D89/L89-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MB003838</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Peach Brightening Set</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-brightening-set</t>
+        </is>
+      </c>
+      <c r="L90" s="2">
+        <f>ROUND(H90*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M90" s="6">
+        <f>IF(OR(D90="",L90=""),"",D90/L90-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MB002665</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Redness Soothing Duo: tônico Azelaic 3 Cica + sérum de ácido azelaico 10%</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Redness Soothing Duo</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/redness-soothing-duo</t>
+        </is>
+      </c>
+      <c r="L91" s="2">
+        <f>ROUND(H91*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M91" s="6">
+        <f>IF(OR(D91="",L91=""),"",D91/L91-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MB003856</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skin Recovery Duo</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/skin-recovery-duo</t>
+        </is>
+      </c>
+      <c r="L92" s="2">
+        <f>ROUND(H92*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M92" s="6">
+        <f>IF(OR(D92="",L92=""),"",D92/L92-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MB002652</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Spotless Skin Duo: sérum de niacinamida + TXA e sérum de ácido azelaico</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spotless Skin Duo</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/ultimate-spot-duo</t>
+        </is>
+      </c>
+      <c r="L93" s="2">
+        <f>ROUND(H93*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M93" s="6">
+        <f>IF(OR(D93="",L93=""),"",D93/L93-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MB003842</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L94" s="2">
+        <f>ROUND(H94*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M94" s="6">
+        <f>IF(OR(D94="",L94=""),"",D94/L94-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MB003875</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
+        </is>
+      </c>
+      <c r="L95" s="2">
+        <f>ROUND(H95*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M95" s="6">
+        <f>IF(OR(D95="",L95=""),"",D95/L95-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MB003868</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1821.9</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>PDRN Glow Boost Full Routine Set</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+        </is>
+      </c>
+      <c r="L96" s="2">
+        <f>ROUND(H96*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M96" s="6">
+        <f>IF(OR(D96="",L96=""),"",D96/L96-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MB002689</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sérum Facial em Spray PDRN Collagen Glow</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Glow Facial Serum Spray</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+        </is>
+      </c>
+      <c r="L97" s="2">
+        <f>ROUND(H97*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M97" s="6">
+        <f>IF(OR(D97="",L97=""),"",D97/L97-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MB002672</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sérum Peach 70% Niacinamida</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Peach 70% Niacinamide Serum</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I98" s="4" t="n"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
+        </is>
+      </c>
+      <c r="L98" s="2">
+        <f>ROUND(H98*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M98" s="6">
+        <f>IF(OR(D98="",L98=""),"",D98/L98-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MB003843</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Golden Honmoon Ceramide Barrier Collagen Mask: máscara de colágeno (4 un.)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I99" s="4" t="n"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+        </is>
+      </c>
+      <c r="L99" s="2">
+        <f>ROUND(H99*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M99" s="6">
+        <f>IF(OR(D99="",L99=""),"",D99/L99-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MB002711</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Heartleaf 70 Soothing Collagen Mask: máscara calmante de colágeno (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Heartleaf 70 Soothing Collagen Mask</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-70-soothing-collagen-mask</t>
+        </is>
+      </c>
+      <c r="L100" s="2">
+        <f>ROUND(H100*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M100" s="6">
+        <f>IF(OR(D100="",L100=""),"",D100/L100-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MB002687</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Melting Patch For Glass Skin: adesivo de colágeno para o rosto (4 un.)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Melting Patch For Glass Skin 4ea</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I101" s="4" t="n"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-glass-skin-4ea-1</t>
+        </is>
+      </c>
+      <c r="L101" s="2">
+        <f>ROUND(H101*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M101" s="6">
+        <f>IF(OR(D101="",L101=""),"",D101/L101-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MB003844</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Melting Patch For Neck: adesivo de colágeno para o pescoço (4 un.)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PDRN Collagen Melting Patch For Neck 4ea</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-neck-4ea-1</t>
+        </is>
+      </c>
+      <c r="L102" s="2">
+        <f>ROUND(H102*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M102" s="6">
+        <f>IF(OR(D102="",L102=""),"",D102/L102-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MB003825</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Peach 70 Niacin Brightening Collagen Mask: máscara iluminadora de colágeno (4 un.)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Peach 70 Niacin Brightening Collagen Mask</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-70-niacin-brightening-collagen-mask-1</t>
+        </is>
+      </c>
+      <c r="L103" s="2">
+        <f>ROUND(H103*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M103" s="6">
+        <f>IF(OR(D103="",L103=""),"",D103/L103-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MB003827</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rice 70 Glow Collagen Mask: máscara de colágeno com arroz (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Rice 70 Glow Collagen Mask</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
+        </is>
+      </c>
+      <c r="L104" s="2">
+        <f>ROUND(H104*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M104" s="6">
+        <f>IF(OR(D104="",L104=""),"",D104/L104-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MB002713</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I105" s="4" t="n"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+        </is>
+      </c>
+      <c r="L105" s="2">
+        <f>ROUND(H105*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M105" s="6">
+        <f>IF(OR(D105="",L105=""),"",D105/L105-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MB003863</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+        </is>
+      </c>
+      <c r="L106" s="2">
+        <f>ROUND(H106*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M106" s="6">
+        <f>IF(OR(D106="",L106=""),"",D106/L106-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MB004044</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml (kit com 2)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>437.9</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
+        </is>
+      </c>
+      <c r="L107" s="2">
+        <f>ROUND(H107*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M107" s="6">
+        <f>IF(OR(D107="",L107=""),"",D107/L107-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MB003855</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7-Day Ultimate Glass Glow Set: rotina glass skin em 7 passos</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>844.9</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>7-Day Glass Skin Set</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/7-day-glass-skin-set</t>
+        </is>
+      </c>
+      <c r="L108" s="2">
+        <f>ROUND(H108*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M108" s="6">
+        <f>IF(OR(D108="",L108=""),"",D108/L108-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MB002729</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Azelaic 10 &amp; Hyaluronic Redness Calming Disk</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Azelaic 10 Hyaluron Redness Soothing Pad</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/azelaic-10-hyaluron-redness-soothing-pad</t>
+        </is>
+      </c>
+      <c r="L109" s="2">
+        <f>ROUND(H109*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M109" s="6">
+        <f>IF(OR(D109="",L109=""),"",D109/L109-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MB002720</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Creme Gua Sha Refinador de Colágeno e Retinol</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Collagen Retinol Refining Gua Sha Cream</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I110" s="4" t="n"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
+        </is>
+      </c>
+      <c r="L110" s="2">
+        <f>ROUND(H110*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M110" s="6">
+        <f>IF(OR(D110="",L110=""),"",D110/L110-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MB002691</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Disco Glow PDRN 100 e Ácido Hialurônico</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I111" s="4" t="n"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
+        </is>
+      </c>
+      <c r="L111" s="2">
+        <f>ROUND(H111*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M111" s="6">
+        <f>IF(OR(D111="",L111=""),"",D111/L111-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MB003817</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Heartleaf Low pH Deep Cleansing Water: água de limpeza de pH baixo</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
+        </is>
+      </c>
+      <c r="L112" s="2">
+        <f>ROUND(H112*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M112" s="6">
+        <f>IF(OR(D112="",L112=""),"",D112/L112-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MB002692</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PDRN 100 Tônico Booster e Ácido Hialurônico</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+        </is>
+      </c>
+      <c r="L113" s="2">
+        <f>ROUND(H113*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M113" s="6">
+        <f>IF(OR(D113="",L113=""),"",D113/L113-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MB002696</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sérum Renovador Nano Retinol™ 0,3% + Niacina</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I114" s="4" t="n"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+        </is>
+      </c>
+      <c r="L114" s="2">
+        <f>ROUND(H114*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M114" s="6">
+        <f>IF(OR(D114="",L114=""),"",D114/L114-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MB003870</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Duo Essencial Diário PDRN</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I115" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
+        </is>
+      </c>
+      <c r="L115" s="2">
+        <f>ROUND(H115*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M115" s="6">
+        <f>IF(OR(D115="",L115=""),"",D115/L115-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MB002653</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Duo de Recuperação para a Pele</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Double Cleansing Duo Set of 2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+        </is>
+      </c>
+      <c r="L116" s="2">
+        <f>ROUND(H116*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M116" s="6">
+        <f>IF(OR(D116="",L116=""),"",D116/L116-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MB002704</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Heartleaf LHA Hydrating Exfoliant Gel</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Heartleaf LHA Moisture Peeling Gel</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I117" s="4" t="n"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
+        </is>
+      </c>
+      <c r="L117" s="2">
+        <f>ROUND(H117*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M117" s="6">
+        <f>IF(OR(D117="",L117=""),"",D117/L117-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MB002731</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hidrating Gentle Cleanser with 8 Hyaluronic Acids</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>8 Hyaluronic Acid Moisturizing Gentle Gel Cleanser</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I118" s="4" t="n"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/8-hyaluronic-acid-moisturizing-gentle-gel-cleanser</t>
+        </is>
+      </c>
+      <c r="L118" s="2">
+        <f>ROUND(H118*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M118" s="6">
+        <f>IF(OR(D118="",L118=""),"",D118/L118-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MB002668</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Kit Iluminador Peach</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Peach Brightening Set</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I119" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-brightening-set</t>
+        </is>
+      </c>
+      <c r="L119" s="2">
+        <f>ROUND(H119*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M119" s="6">
+        <f>IF(OR(D119="",L119=""),"",D119/L119-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MB002682</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kit Rotina Completa PDRN Glow Boost</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>1821.9</v>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>PDRN Glow Boost Full Routine Set</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+        </is>
+      </c>
+      <c r="L120" s="2">
+        <f>ROUND(H120*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M120" s="6">
+        <f>IF(OR(D120="",L120=""),"",D120/L120-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MB002712</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Loção Diária Heartleaf 70</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Heartleaf 70 Daily Lotion</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
+        </is>
+      </c>
+      <c r="L121" s="2">
+        <f>ROUND(H121*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M121" s="6">
+        <f>IF(OR(D121="",L121=""),"",D121/L121-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MB002661</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Máscara de Colágeno Rice 70 Glow</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Rice 70 Glow Collagen Mask</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
+        </is>
+      </c>
+      <c r="L122" s="2">
+        <f>ROUND(H122*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M122" s="6">
+        <f>IF(OR(D122="",L122=""),"",D122/L122-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MB002676</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sérum Labial PDRN</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>PDRN Lip Serum</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-lip-serum</t>
+        </is>
+      </c>
+      <c r="L123" s="2">
+        <f>ROUND(H123*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M123" s="6">
+        <f>IF(OR(D123="",L123=""),"",D123/L123-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MB003841</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tônico Booster PDRN 100 com Ácido Hialurônico</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+        </is>
+      </c>
+      <c r="L124" s="2">
+        <f>ROUND(H124*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M124" s="6">
+        <f>IF(OR(D124="",L124=""),"",D124/L124-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MB002660</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Tônico Leitoso Rice 70 Glow</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rice 70 Glow Milky Toner</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
+        </is>
+      </c>
+      <c r="L125" s="2">
+        <f>ROUND(H125*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M125" s="6">
+        <f>IF(OR(D125="",L125=""),"",D125/L125-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MB003857</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Adesivo Derretível de Colágeno PDRN para Pescoço (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MB002650</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Adesivo Ultrafino para Acne</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="L127" s="2" t="n"/>
+      <c r="M127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MB002686</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Adesivo de Colágeno PDRN para o Pescoço (4 unidades)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MB003994</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Anua Kit de Patches Firmadores Melting com Colágeno PDRN</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MB002699</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Bastão Solar com Acabamento Glow Invisível</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MB002733</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Calming Pad 8 Tipos de Ácido Hialurônico e Catequina</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MB002738</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Creme Barreira com 3 Ceramidas e Pantenol</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MB002670</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Creme Enriquecido de Pêssego 77 Niacinamida</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="n"/>
+      <c r="L133" s="2" t="n"/>
+      <c r="M133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MB002694</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Disco Iluminador Niacinamida 5 e TXA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MB002721</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Duo de Cuidado para Acne</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="L135" s="2" t="n"/>
+      <c r="M135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MB003812</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Espuma de Limpeza Profunda para Poros com Heartleaf e Quercetinol</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="L136" s="2" t="n"/>
+      <c r="M136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MB002732</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Espuma de Limpeza Suave Hidratante com 8 Ácidos Hialurônicos</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="L137" s="2" t="n"/>
+      <c r="M137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MB002710</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Heartleaf 70% Creme Calmante Intenso</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="4" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MB003839</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Kit Completo Nutritivo de Arroz para Pele Seca</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="n"/>
+      <c r="L139" s="2" t="n"/>
+      <c r="M139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MB002690</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Kit PDRN 4 Passos Pele Luminosa</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>874.9</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="n"/>
+      <c r="L140" s="2" t="n"/>
+      <c r="M140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MB003860</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Kit PDRN Glowy Skin 4 Passos</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>874.9</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="n"/>
+      <c r="L141" s="2" t="n"/>
+      <c r="M141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MB003873</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Kit PDRN Luminosidade Radiante o Dia Todo</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MB002735</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kit Rotina 7 Dias Manchas Escuras</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1012.9</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="L143" s="2" t="n"/>
+      <c r="M143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MB002730</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Kit Rotina Antienvelhecimento</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>838.9</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MB002734</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Kit Rotina Refino de Poros 7 Dias</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="L145" s="2" t="n"/>
+      <c r="M145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MB002736</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Kit Rotina de 7 Dias para Controle da Acne</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MB003866</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Leite Condicionador de Pêssego 77 Niacina</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="L147" s="2" t="n"/>
+      <c r="M147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MB002659</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Loção Hidratante Intensiva Rice 70</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MB002671</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Loção Leitosa de Niacina Peach 77</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="L149" s="2" t="n"/>
+      <c r="M149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MB002673</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Máscara Iluminadora de Colágeno Peach 70 e Niacina</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MB003826</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Máscara de Colágeno Calmante com Houttuynia Cordata 70</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="n"/>
+      <c r="L151" s="2" t="n"/>
+      <c r="M151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MB002693</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Niacinamide e Ácido Tranexâmico Tônico Booster Iluminador</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MB002677</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PDRN e Ácido Hialurônico Espuma de Limpeza Hidratante</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="6" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MB003830</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Patch Microagulhado para Tratamento de Espinhas com Tríplice Ácido</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MB002657</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Pó de Limpeza Iluminador de Enzima de Arroz</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="n"/>
+      <c r="I155" s="4" t="n"/>
+      <c r="L155" s="2" t="n"/>
+      <c r="M155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MB002658</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sérum Hidratante Fortalecedor da Barreira de Pele com Ceramidas de Arroz 7</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n"/>
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MB003840</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sérum PDRN Cápsula 100 de Ácido Hialurônico – Dose Única</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n"/>
+      <c r="L157" s="2" t="n"/>
+      <c r="M157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MB003867</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Tônico Booster Iluminador com Niacinamida e Ácido Tranexâmico</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MB002728</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Tônico Clareador Azelaico 3 Cica</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="n"/>
+      <c r="I159" s="4" t="n"/>
+      <c r="L159" s="2" t="n"/>
+      <c r="M159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MB002722</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Tônico Esfoliante BHA 2%</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="n"/>
+      <c r="I160" s="4" t="n"/>
+      <c r="L160" s="2" t="n"/>
+      <c r="M160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MB003845</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tônico Essência de Pêssego 77 com Niacinamida</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="n"/>
+      <c r="L161" s="2" t="n"/>
+      <c r="M161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>MB002703</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Água de Limpeza Profunda Low pH Heartleaf</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D162" s="2" t="n">
         <v>159.9</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>Sem par</t>
         </is>
       </c>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="6" t="n"/>
+      <c r="H162" s="4" t="n"/>
+      <c r="I162" s="4" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MB002702</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Óleo de Limpeza Suave de Poros Heartleaf</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="n"/>
+      <c r="L163" s="2" t="n"/>
+      <c r="M163" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4631,10 +8406,67 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId68"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8743,7 +12575,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:03 UTC</t>
+          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-Anua.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Anua.xlsx
@@ -1534,12 +1534,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB002716</t>
+          <t>MB002718</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Even Tone &amp; Barrier Set: discos TXA + sérum de niacinamida + creme de ceramidas</t>
+          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 2 Sets(+Gifts)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>503.9</v>
+        <v>437.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1557,15 +1557,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Even Tone &amp; Barrier Set</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Double Cleansing Duo Set</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2 Sets(+Gifts)</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>62.5</v>
+        <v>78</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1574,7 +1578,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/even-tone-barrier-set</t>
+          <t>https://anua.us/products/double-cleansing-duo-set-2?variant=51329149010198</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1589,12 +1593,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB002715</t>
+          <t>MB002716</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Even Tone &amp; Pore Refining Duo: tônico BHA 2% + sérum de niacinamida e TXA</t>
+          <t>Even Tone &amp; Barrier Set: discos TXA + sérum de niacinamida + creme de ceramidas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1603,7 +1607,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>313.9</v>
+        <v>503.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1612,15 +1616,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Even tone &amp; Pore Refining Duo</t>
+          <t>Even Tone &amp; Barrier Set</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>43</v>
+        <v>62.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1629,7 +1633,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/even-tone-pore-refining-duo</t>
+          <t>https://anua.us/products/even-tone-barrier-set</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1644,12 +1648,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB002666</t>
+          <t>MB002715</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Complete Set</t>
+          <t>Even Tone &amp; Pore Refining Duo: tônico BHA 2% + sérum de niacinamida e TXA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1658,7 +1662,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>481.9</v>
+        <v>313.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1667,15 +1671,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set</t>
+          <t>Even tone &amp; Pore Refining Duo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
+          <t>https://anua.us/products/even-tone-pore-refining-duo</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1699,12 +1703,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB002667</t>
+          <t>MB002666</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
+          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Complete Set</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1725,7 +1729,11 @@
           <t>Fall into Deep Hydration Set</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Complete Set</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="n">
         <v>143</v>
       </c>
@@ -1739,7 +1747,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/amazon-x-tiktok-viral-routine-kit</t>
+          <t>https://anua.us/products/fall-into-deep-hydration-essential-set?variant=67740819030294</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1754,12 +1762,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003823</t>
+          <t>MB002667</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
+          <t>Fall into Deep Hydration Set: rotina viral com PDRN e retinol · Essential Set</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1768,7 +1776,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>188.9</v>
+        <v>481.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1777,14 +1785,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Fall into Deep Hydration Set</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Essential Set</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I24" s="4" t="n"/>
+        <v>124</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>176</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1792,7 +1806,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
+          <t>https://anua.us/products/fall-into-deep-hydration-essential-set?variant=67716215898390</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1807,12 +1821,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003809</t>
+          <t>MB003823</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
+          <t>Heartleaf 70 Daily Lotion: loção hidratante leve com heartleaf 200 ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1830,7 +1844,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Intense Calming Cream</t>
+          <t>Heartleaf 70 Daily Lotion</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1845,7 +1859,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
+          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1860,12 +1874,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB002709</t>
+          <t>MB003809</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad: discos tônicos com heartleaf e PHA (70 unidades)</t>
+          <t>Heartleaf 70% Intense Calming Cream: creme calmante com ceramida 50 ml</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1874,7 +1888,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>166.9</v>
+        <v>188.9</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1883,12 +1897,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>Heartleaf 70% Intense Calming Cream</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
@@ -1898,7 +1912,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
+          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1913,12 +1927,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB002707</t>
+          <t>MB002709</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 250ml</t>
+          <t>Heartleaf 77 Clear Pad: discos tônicos com heartleaf e PHA (70 unidades)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1936,14 +1950,10 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Soothing Toner</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+          <t>Heartleaf 77 Clear Pad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
         <v>23</v>
       </c>
@@ -1955,7 +1965,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356121366</t>
+          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -1970,12 +1980,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB002708</t>
+          <t>MB002707</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 500ml</t>
+          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 250ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1984,7 +1994,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>250.9</v>
+        <v>166.9</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1998,11 +2008,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>34.5</v>
+        <v>23</v>
       </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" t="inlineStr">
@@ -2012,7 +2022,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356154134</t>
+          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356121366</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2027,12 +2037,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB002706</t>
+          <t>MB002708</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
+          <t>Heartleaf 77 Soothing Toner: tônico calmante com 77% de heartleaf · 500ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2041,7 +2051,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>159.9</v>
+        <v>250.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -2050,12 +2060,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Heartleaf 77 Soothing Toner</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="n">
-        <v>22</v>
+        <v>34.5</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
@@ -2065,7 +2079,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
+          <t>https://anua.us/products/heartleaf-77-soothing-toner-1?variant=51655356154134</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2080,12 +2094,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003832</t>
+          <t>MB002706</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule: ampola calmante e hidratante 30 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2094,7 +2108,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>160.9</v>
+        <v>159.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -2103,7 +2117,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream</t>
+          <t>Heartleaf 80% Moisture Soothing Ampoule</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2118,7 +2132,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
+          <t>https://anua.us/products/heartleaf-80-moisture-soothing-ampoule-30ml</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2133,12 +2147,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003813</t>
+          <t>MB003832</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
+          <t>Heartleaf Centella Red Spot Cream: creme calmante para pontinhos vermelhos 30 g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2147,7 +2161,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>159.9</v>
+        <v>160.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -2156,7 +2170,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel</t>
+          <t>Heartleaf Centella Red Spot Cream</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2171,7 +2185,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
+          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2186,12 +2200,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003811</t>
+          <t>MB003813</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
+          <t>Heartleaf LHA Moisture Peeling Gel: gel esfoliante suave com LHA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2209,7 +2223,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Heartleaf LHA Moisture Peeling Gel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -2224,7 +2238,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2239,12 +2253,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003871</t>
+          <t>MB003811</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
+          <t>Heartleaf Pore Control Cleansing Oil: óleo de limpeza para os poros 200 ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2253,7 +2267,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>130.9</v>
+        <v>159.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -2262,12 +2276,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Invisible Glow Finish Sunstick</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I33" s="4" t="n"/>
       <c r="J33" t="inlineStr">
@@ -2277,7 +2291,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2292,12 +2306,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB002698</t>
+          <t>MB003871</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Invisible Matte Finish Sunscreen: protetor solar matte FPS 50 50 ml</t>
+          <t>Invisible Glow Finish Sunstick: protetor solar em bastão FPS 50 17,5 g</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,7 +2320,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>160.9</v>
+        <v>130.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -2315,12 +2329,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Invisible Matte Finish Sunscreen</t>
+          <t>Invisible Glow Finish Sunstick</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" t="inlineStr">
@@ -2330,7 +2344,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/invisible-matte-finish-sunscreen</t>
+          <t>https://anua.us/products/invisible-glow-finish-sunstick-1</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2345,12 +2359,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003872</t>
+          <t>MB002698</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
+          <t>Invisible Matte Finish Sunscreen: protetor solar matte FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2359,7 +2373,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>130.9</v>
+        <v>160.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -2368,12 +2382,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen</t>
+          <t>Invisible Matte Finish Sunscreen</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
@@ -2383,7 +2397,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
+          <t>https://anua.us/products/invisible-matte-finish-sunscreen</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2398,12 +2412,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003835</t>
+          <t>MB003872</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
+          <t>Mineral Weightless Finish Sunscreen: protetor solar mineral FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2412,7 +2426,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>166.9</v>
+        <v>130.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -2421,12 +2435,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Niacinamide 5 TXA Brightening Pad</t>
+          <t>Mineral Weightless Finish Sunscreen</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I36" s="4" t="n"/>
       <c r="J36" t="inlineStr">
@@ -2436,7 +2450,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
+          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2451,12 +2465,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003859</t>
+          <t>MB003835</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
+          <t>Niacinamide 5 TXA Brightening Pad: discos iluminadores (60 unidades)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2465,7 +2479,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>152.9</v>
+        <v>166.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -2474,12 +2488,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>Niacinamide 5 TXA Brightening Pad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2489,7 +2503,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/niacinamide-5-txa-brightening-pad</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2504,12 +2518,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003834</t>
+          <t>MB003859</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner: tônico hidratante de PDRN 250 ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2518,7 +2532,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>166.9</v>
+        <v>152.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -2527,12 +2541,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
@@ -2542,7 +2556,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2557,12 +2571,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB002688</t>
+          <t>MB003834</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray Mini: bruma sérum de PDRN 30 ml</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad: discos hidratantes de PDRN (60 unidades)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2571,7 +2585,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>144.9</v>
+        <v>166.9</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -2580,12 +2594,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
@@ -2595,7 +2609,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2610,12 +2624,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB002684</t>
+          <t>MB002688</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Full Care Set</t>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini: bruma sérum de PDRN 30 ml</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2624,7 +2638,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>742.9</v>
+        <v>144.9</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -2633,20 +2647,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Full Care Set</t>
-        </is>
-      </c>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>124</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2654,7 +2662,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2669,12 +2677,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB002685</t>
+          <t>MB003876</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Trial Set</t>
+          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2683,7 +2691,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>502.9</v>
+        <v>210.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -2692,20 +2700,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Full Care Set</t>
-        </is>
-      </c>
+          <t>PDRN Collagen Glow Facial Serum Spray</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>124</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I41" s="4" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2713,7 +2715,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2728,12 +2730,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB002683</t>
+          <t>MB002684</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDRN Deep Hydrating Prep &amp; Boost Duo: discos de PDRN + sérum de PDRN 30 ml</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Full Care Set</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2742,7 +2744,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>350.9</v>
+        <v>742.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -2751,15 +2753,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2768,7 +2774,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2783,12 +2789,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003853</t>
+          <t>MB002685</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set: spray de PDRN + adesivos de colágeno · Trial Set</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2797,7 +2803,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1821.9</v>
+        <v>502.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -2806,16 +2812,18 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Trial Set</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>333.8</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I43" s="4" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2823,7 +2831,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=51200377520406</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2838,12 +2846,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB002681</t>
+          <t>MB002683</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo: discos de PDRN + sérum de PDRN 30 ml</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2852,7 +2860,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>225.9</v>
+        <v>350.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2861,14 +2869,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I44" s="4" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2876,7 +2886,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
+          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2891,12 +2901,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB002680</t>
+          <t>MB003853</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum: sérum de PDRN com cápsulas</t>
+          <t>PDRN Glow Boost Full Routine Set: rotina completa de PDRN em 7 produtos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2905,7 +2915,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>181.9</v>
+        <v>1821.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -2914,14 +2924,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum</t>
+          <t>PDRN Glow Boost Full Routine Set</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I45" s="4" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>333.8</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2929,7 +2941,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-one-day-serum</t>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2944,12 +2956,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB002678</t>
+          <t>MB002681</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask: máscara de PDRN (2 caixas de 10)</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream: creme hidratante de PDRN 60 ml</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2958,7 +2970,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>209.9</v>
+        <v>225.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -2967,16 +2979,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask</t>
+          <t>PDRN Hyaluronic Acid 100 Moisturizing Cream</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>57.6</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2984,7 +2994,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-mask</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-100-moisturizing-cream-1</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -2999,12 +3009,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003862</t>
+          <t>MB002680</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum: sérum de PDRN com cápsulas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3013,7 +3023,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>108.9</v>
+        <v>181.9</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -3022,12 +3032,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 One Day Serum</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47" t="inlineStr">
@@ -3037,7 +3047,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-one-day-serum</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3052,12 +3062,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003861</t>
+          <t>MB002678</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask: máscara de PDRN (2 caixas de 10)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3066,7 +3076,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>209.9</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -3075,14 +3085,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum Mask</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I48" s="4" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>57.6</v>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3090,7 +3102,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-lip-serum</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-mask</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3105,12 +3117,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB002675</t>
+          <t>MB003862</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam: espuma de limpeza hidratante 150 ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3119,7 +3131,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>663.9</v>
+        <v>108.9</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -3128,16 +3140,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" t="inlineStr">
@@ -3147,7 +3155,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3162,12 +3170,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB002674</t>
+          <t>MB003861</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
+          <t>PDRN Lip Serum: sérum labial hidratante com PDRN 10 ml</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3176,7 +3184,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>765.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -3185,16 +3193,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PDRN Plump &amp; Dewy Glow Set</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Basic Set</t>
-        </is>
-      </c>
+          <t>PDRN Lip Serum</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="I50" s="4" t="n"/>
       <c r="J50" t="inlineStr">
@@ -3204,7 +3208,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
+          <t>https://anua.us/products/pdrn-lip-serum</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3219,12 +3223,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003810</t>
+          <t>MB002675</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Basic Set</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3233,7 +3237,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>159.9</v>
+        <v>663.9</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -3242,12 +3246,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Basic Set</t>
+        </is>
+      </c>
       <c r="H51" s="4" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
@@ -3257,7 +3265,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018038550</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3272,12 +3280,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003846</t>
+          <t>MB002674</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
+          <t>PDRN Plump &amp; Dewy Glow Set: sérum em spray + creme com PDRN · Special Value Set</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3286,7 +3294,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>181.9</v>
+        <v>765.9</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -3295,14 +3303,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Conditioning Milk</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>PDRN Plump &amp; Dewy Glow Set</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Special Value Set</t>
+        </is>
+      </c>
       <c r="H52" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I52" s="4" t="n"/>
+        <v>105</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>152</v>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3310,7 +3324,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
+          <t>https://anua.us/products/pdrn-all-day-dewy-glow-set?variant=51405018005782</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3325,12 +3339,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003824</t>
+          <t>MB003810</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
+          <t>Peach 70% Niacinamide Serum: sérum de pêssego e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3339,7 +3353,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>188.9</v>
+        <v>159.9</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -3348,12 +3362,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Enriched Cream</t>
+          <t>Peach 70% Niacinamide Serum</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I53" s="4" t="n"/>
       <c r="J53" t="inlineStr">
@@ -3363,7 +3377,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
+          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3378,12 +3392,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB002669</t>
+          <t>MB003846</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Essence Toner: tônico essência de pêssego 250 ml</t>
+          <t>Peach 77 Niacin Conditioning Milk: loção leitosa de pêssego 150 ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3401,7 +3415,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Peach 77 Niacin Essence Toner</t>
+          <t>Peach 77 Niacin Conditioning Milk</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3416,7 +3430,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-77-niacin-essence-toner-1</t>
+          <t>https://anua.us/products/peach-77-niacin-conditioning-milk</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3431,12 +3445,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB002664</t>
+          <t>MB003824</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Redness Soothing Prep &amp; Boost Duo: discos + sérum de ácido azelaico</t>
+          <t>Peach 77 Niacin Enriched Cream: creme de pêssego e niacinamida 50 ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3445,7 +3459,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>327.9</v>
+        <v>188.9</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3454,16 +3468,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Redness Soothing Prep &amp; Boost Duo</t>
+          <t>Peach 77 Niacin Enriched Cream</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>51</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I55" s="4" t="n"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3471,7 +3483,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-pad-serum-duo</t>
+          <t>https://anua.us/products/peach-77-niacin-enriched-cream-1</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3486,12 +3498,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB002663</t>
+          <t>MB002669</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Retinol 0,1 Caffeine Revitalizing Eye Cream: creme para os olhos 30 ml</t>
+          <t>Peach 77 Niacin Essence Toner: tônico essência de pêssego 250 ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3500,7 +3512,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>166.9</v>
+        <v>181.9</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3509,12 +3521,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
+          <t>Peach 77 Niacin Essence Toner</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
@@ -3524,7 +3536,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
+          <t>https://anua.us/products/peach-77-niacin-essence-toner-1</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3539,12 +3551,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB002662</t>
+          <t>MB002664</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Retinol Anti-Aging Duo: sérum de retinol 0,3% + creme de olhos com retinol</t>
+          <t>Redness Soothing Prep &amp; Boost Duo: discos + sérum de ácido azelaico</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3553,7 +3565,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>320.9</v>
+        <v>327.9</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -3562,7 +3574,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Retinol Anti-Aging Duo</t>
+          <t>Redness Soothing Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3570,7 +3582,7 @@
         <v>44</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3579,7 +3591,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/retinol-anti-aging-duo</t>
+          <t>https://anua.us/products/azelaic-pad-serum-duo</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3594,12 +3606,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003816</t>
+          <t>MB002663</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
+          <t>Retinol 0,1 Caffeine Revitalizing Eye Cream: creme para os olhos 30 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3617,7 +3629,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner</t>
+          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3632,7 +3644,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
+          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3647,12 +3659,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB003831</t>
+          <t>MB002662</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
+          <t>Retinol Anti-Aging Duo: sérum de retinol 0,3% + creme de olhos com retinol</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3661,7 +3673,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>144.9</v>
+        <v>320.9</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -3670,14 +3682,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rice 70 Intensive Moisturizing Milk</t>
+          <t>Retinol Anti-Aging Duo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I59" s="4" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>47</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3685,7 +3699,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
+          <t>https://anua.us/products/retinol-anti-aging-duo</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3700,12 +3714,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB003819</t>
+          <t>MB003816</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
+          <t>Rice 70 Glow Milky Toner: tônico leitoso de arroz 250 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3723,7 +3737,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
+          <t>Rice 70 Glow Milky Toner</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3738,7 +3752,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
+          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3753,12 +3767,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003818</t>
+          <t>MB003831</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
+          <t>Rice 70 Intensive Moisturizing Milk: loção hidratante de arroz 150 ml</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3776,7 +3790,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rice Enzyme Brightening Cleansing Powder</t>
+          <t>Rice 70 Intensive Moisturizing Milk</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3791,7 +3805,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
+          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3806,12 +3820,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB002656</t>
+          <t>MB003819</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rice Nourishing Full Set: rotina de arroz em 5 passos para pele seca</t>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum: sérum de arroz e ceramida 50 ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3820,7 +3834,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>680.9</v>
+        <v>166.9</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -3829,16 +3843,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rice Nourishing Full Set for Dry Skin</t>
+          <t>Rice Ceramide 7 Hydrating Barrier Serum</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>108</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I62" s="4" t="n"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3846,7 +3858,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-glow-full-set</t>
+          <t>https://anua.us/products/rice-ceramide-7-hydrating-barrier-serum</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3861,12 +3873,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB002655</t>
+          <t>MB003818</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas (55 unidades)</t>
+          <t>Rice Enzyme Brightening Cleansing Powder: pó de limpeza enzimático de arroz 40 g</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3875,7 +3887,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>102.9</v>
+        <v>144.9</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -3884,12 +3896,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rumi Ultra-thin Spot Cover Patch (55ea)</t>
+          <t>Rice Enzyme Brightening Cleansing Powder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I63" s="4" t="n"/>
       <c r="J63" t="inlineStr">
@@ -3899,7 +3911,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-55ea</t>
+          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3914,12 +3926,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB002654</t>
+          <t>MB002656</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas com estojo (28 un.)</t>
+          <t>Rice Nourishing Full Set: rotina de arroz em 5 passos para pele seca</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3928,7 +3940,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>102.9</v>
+        <v>680.9</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -3937,14 +3949,16 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rumi Ultra-thin Spot Cover Patch with Case (28ea)</t>
+          <t>Rice Nourishing Full Set for Dry Skin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I64" s="4" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>108</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3952,7 +3966,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-with-case-28ea</t>
+          <t>https://anua.us/products/rice-glow-full-set</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -3967,12 +3981,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB002651</t>
+          <t>MB002655</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Triple Acid Spot Care Microdart Patch: adesivo localizado com microdarts (12 un.)</t>
+          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas (55 unidades)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3981,7 +3995,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>108.9</v>
+        <v>102.9</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -3990,12 +4004,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Triple Acid Spot Care Microdart Patch</t>
+          <t>Rumi Ultra-thin Spot Cover Patch (55ea)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I65" s="4" t="n"/>
       <c r="J65" t="inlineStr">
@@ -4005,7 +4019,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/triple-acid-spot-care-microdart-patch-1</t>
+          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-55ea</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4020,12 +4034,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB003829</t>
+          <t>MB002654</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
+          <t>Rumi Ultra-thin Spot Cover Patch: adesivos para espinhas com estojo (28 un.)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4034,7 +4048,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>123.9</v>
+        <v>102.9</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -4043,12 +4057,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ultra-Thin Spot Cover Patch</t>
+          <t>Rumi Ultra-thin Spot Cover Patch with Case (28ea)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I66" s="4" t="n"/>
       <c r="J66" t="inlineStr">
@@ -4058,7 +4072,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
+          <t>https://anua.us/products/rumi-ultra-thin-spot-cover-patch-with-case-28ea</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4073,12 +4087,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB002649</t>
+          <t>MB002651</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Youthful Glow Set for over 30+: rotina de 5 passos com PDRN e retinol</t>
+          <t>Triple Acid Spot Care Microdart Patch: adesivo localizado com microdarts (12 un.)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4087,7 +4101,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>742.9</v>
+        <v>108.9</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -4096,16 +4110,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Youthful Glow Set for over 30+</t>
+          <t>Triple Acid Spot Care Microdart Patch</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>124</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4113,7 +4125,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/black-friday-exclusive-set-special-gift-30-sheet-masks</t>
+          <t>https://anua.us/products/triple-acid-spot-care-microdart-patch-1</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4128,12 +4140,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003864</t>
+          <t>MB003829</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
+          <t>Ultra-Thin Spot Cover Patch: adesivos invisíveis para espinhas (75 unidades)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4142,7 +4154,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>131.9</v>
+        <v>123.9</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -4151,12 +4163,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen</t>
+          <t>Ultra-Thin Spot Cover Patch</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I68" s="4" t="n"/>
       <c r="J68" t="inlineStr">
@@ -4166,7 +4178,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
+          <t>https://anua.us/products/ultra-thin-spot-cover-patch</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4181,21 +4193,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003808</t>
+          <t>MB002649</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>Youthful Glow Set for over 30+: rotina de 5 passos com PDRN e retinol</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>166.9</v>
+        <v>742.9</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -4204,14 +4216,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Heartleaf 77 Clear Pad</t>
+          <t>Youthful Glow Set for over 30+</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I69" s="4" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4219,7 +4233,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
+          <t>https://anua.us/products/black-friday-exclusive-set-special-gift-30-sheet-masks</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4234,21 +4248,21 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB002701</t>
+          <t>MB003864</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen: protetor solar hidratante FPS 50 50 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>144.9</v>
+        <v>131.9</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -4257,12 +4271,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" s="4" t="n"/>
       <c r="J70" t="inlineStr">
@@ -4272,7 +4286,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4287,12 +4301,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB002648</t>
+          <t>MB003808</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Moisturizing Finish Zero-cast Sunscreen</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4301,7 +4315,7 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>130.9</v>
+        <v>166.9</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -4310,12 +4324,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zero-cast Moisturizing Finish Sunscreen</t>
+          <t>Heartleaf 77 Clear Pad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I71" s="4" t="n"/>
       <c r="J71" t="inlineStr">
@@ -4325,7 +4339,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
+          <t>https://anua.us/products/heartleaf-77-toner-pad-160ml</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4340,12 +4354,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003858</t>
+          <t>MB002701</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4354,7 +4368,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>502.9</v>
+        <v>144.9</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -4363,20 +4377,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PDRN Collagen Wrinkle Smoothing Set</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Full Care Set</t>
-        </is>
-      </c>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>124</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I72" s="4" t="n"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4384,7 +4392,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4399,12 +4407,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003854</t>
+          <t>MB002648</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
+          <t>Moisturizing Finish Zero-cast Sunscreen</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4413,7 +4421,7 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>166.9</v>
+        <v>130.9</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -4422,12 +4430,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
+          <t>Zero-cast Moisturizing Finish Sunscreen</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I73" s="4" t="n"/>
       <c r="J73" t="inlineStr">
@@ -4437,7 +4445,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
+          <t>https://anua.us/products/zero-cast-moisturizing-finish-sunscreen</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4452,12 +4460,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB002726</t>
+          <t>MB003858</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4466,7 +4474,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>137.9</v>
+        <v>502.9</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -4475,14 +4483,20 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>PDRN Collagen Wrinkle Smoothing Set</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Full Care Set</t>
+        </is>
+      </c>
       <c r="H74" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I74" s="4" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4490,7 +4504,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/pdrn-collagen-wrinkle-smoothing-intensive-set?variant=50904414585110</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4505,12 +4519,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB003865</t>
+          <t>MB003854</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
+          <t>Revitalizing Eye Cream with 0.1% Retinol and Caffeine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4519,7 +4533,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>137.9</v>
+        <v>166.9</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -4528,12 +4542,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
+          <t>Retinol 0.1 Caffeine Revitalizing Eye Cream</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I75" s="4" t="n"/>
       <c r="J75" t="inlineStr">
@@ -4543,7 +4557,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
+          <t>https://anua.us/products/retinol-0-1-caffeine-revitalizing-eye-cream</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4558,39 +4572,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB002737</t>
+          <t>MB002726</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5-step Korean Skincare Set: rotina coreana de 5 passos Heartleaf + TXA</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>706.9</v>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>5-step Korean Skincare Set</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="4" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>119</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I76" s="4" t="n"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4598,7 +4610,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/glass-skin-full-routine-set</t>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
         </is>
       </c>
       <c r="L76" s="2">
@@ -4613,39 +4625,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003833</t>
+          <t>MB003865</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
+          <t>Soothing Moisturizer with Azelaic Acid and CICA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>306.9</v>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Breakout Care Duo</t>
+          <t>Azelaic Acid CICA Skin Soothing Moisturizer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I77" s="4" t="n"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4653,7 +4663,7 @@
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/intensive-spot-care-duo</t>
+          <t>https://anua.us/products/azelaic-acid-cica-skin-soothing-moisturizer</t>
         </is>
       </c>
       <c r="L77" s="2">
@@ -4668,39 +4678,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB002717</t>
+          <t>MB002689</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 1 Set</t>
+          <t>Sérum Facial em Spray PDRN Collagen Glow</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>210.9</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Double Cleansing Duo Set of 2</t>
+          <t>PDRN Collagen Glow Facial Serum Spray</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>114</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I78" s="4" t="n"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4708,7 +4716,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
         </is>
       </c>
       <c r="L78" s="2">
@@ -4723,39 +4731,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB002718</t>
+          <t>MB002676</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 2 Sets(+Gifts)</t>
+          <t>Sérum Labial PDRN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Double Cleansing Duo Set of 2</t>
+          <t>PDRN Lip Serum</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>114</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I79" s="4" t="n"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4763,7 +4769,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+          <t>https://anua.us/products/pdrn-lip-serum</t>
         </is>
       </c>
       <c r="L79" s="2">
@@ -4778,12 +4784,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB002714</t>
+          <t>MB002737</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Glass Skin Essential Set: limpeza dupla Heartleaf + sérum de niacinamida e TXA</t>
+          <t>5-step Korean Skincare Set: rotina coreana de 5 passos Heartleaf + TXA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4792,7 +4798,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>844.9</v>
+        <v>706.9</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -4801,15 +4807,15 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Glass Skin Essential Set</t>
+          <t>5-step Korean Skincare Set</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="4" t="n">
-        <v>66</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4818,7 +4824,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/glass-skin-essential-set</t>
+          <t>https://anua.us/products/glass-skin-full-routine-set</t>
         </is>
       </c>
       <c r="L80" s="2">
@@ -4833,12 +4839,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB002705</t>
+          <t>MB003833</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Redness Cream</t>
+          <t>Breakout Care Duo: sérum de ácido azelaico + creme localizado Heartleaf Centella</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4847,7 +4853,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>159.9</v>
+        <v>306.9</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -4856,14 +4862,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heartleaf Centella Red Spot Cream</t>
+          <t>Breakout Care Duo</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I81" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>50</v>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4871,7 +4879,7 @@
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
+          <t>https://anua.us/products/intensive-spot-care-duo</t>
         </is>
       </c>
       <c r="L81" s="2">
@@ -4886,12 +4894,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB003821</t>
+          <t>MB002717</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
+          <t>Double Cleansing Duo Set: óleo de limpeza + espuma Heartleaf para poros · 1 Set</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4900,7 +4908,7 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>144.9</v>
+        <v>437.9</v>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
@@ -4909,14 +4917,16 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heartleaf Pore Control Cleansing Oil</t>
+          <t>Double Cleansing Duo Set of 2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I82" s="4" t="n"/>
+        <v>78</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>114</v>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4924,7 +4934,7 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
         </is>
       </c>
       <c r="L82" s="2">
@@ -4939,12 +4949,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB002700</t>
+          <t>MB002714</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Heartleaf Quercetinol: espuma de limpeza profunda para os poros 150 ml</t>
+          <t>Glass Skin Essential Set: limpeza dupla Heartleaf + sérum de niacinamida e TXA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4953,7 +4963,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>144.9</v>
+        <v>844.9</v>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
@@ -4962,14 +4972,16 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
+          <t>Glass Skin Essential Set</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I83" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>70</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4977,7 +4989,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
+          <t>https://anua.us/products/glass-skin-essential-set</t>
         </is>
       </c>
       <c r="L83" s="2">
@@ -4992,12 +5004,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB002697</t>
+          <t>MB002705</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Light Finish Mineral Sunscreen</t>
+          <t>Heartleaf Centella Redness Cream</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5006,7 +5018,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>131.9</v>
+        <v>159.9</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
@@ -5015,12 +5027,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mineral Weightless Finish Sunscreen</t>
+          <t>Heartleaf Centella Red Spot Cream</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I84" s="4" t="n"/>
       <c r="J84" t="inlineStr">
@@ -5030,7 +5042,7 @@
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
+          <t>https://anua.us/products/heartleaf-centella-red-spot-cream-1</t>
         </is>
       </c>
       <c r="L84" s="2">
@@ -5045,12 +5057,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB003814</t>
+          <t>MB003821</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
+          <t>Heartleaf Pore Cleansing Oil Mild: óleo de limpeza suave sem fragrância 200 ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5059,7 +5071,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>181.9</v>
+        <v>144.9</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -5068,12 +5080,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I85" s="4" t="n"/>
       <c r="J85" t="inlineStr">
@@ -5083,7 +5095,7 @@
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
         </is>
       </c>
       <c r="L85" s="2">
@@ -5098,12 +5110,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB002695</t>
+          <t>MB002700</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
+          <t>Heartleaf Quercetinol: espuma de limpeza profunda para os poros 150 ml</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5112,7 +5124,7 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>174.9</v>
+        <v>144.9</v>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
@@ -5121,12 +5133,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
+          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I86" s="4" t="n"/>
       <c r="J86" t="inlineStr">
@@ -5136,7 +5148,7 @@
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
+          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
         </is>
       </c>
       <c r="L86" s="2">
@@ -5151,12 +5163,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB003848</t>
+          <t>MB002697</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
+          <t>Light Finish Mineral Sunscreen</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5165,7 +5177,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>152.9</v>
+        <v>131.9</v>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
@@ -5174,12 +5186,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
+          <t>Mineral Weightless Finish Sunscreen</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I87" s="4" t="n"/>
       <c r="J87" t="inlineStr">
@@ -5189,7 +5201,7 @@
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
+          <t>https://anua.us/products/mineral-weightless-finish-sunscreen</t>
         </is>
       </c>
       <c r="L87" s="2">
@@ -5204,12 +5216,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003876</t>
+          <t>MB003814</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray: bruma sérum com PDRN e colágeno 100 ml</t>
+          <t>Nano Retinol 0,3% + Niacin Renewing Serum: sérum de retinol e niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5218,7 +5230,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>210.9</v>
+        <v>181.9</v>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
@@ -5227,12 +5239,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray</t>
+          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I88" s="4" t="n"/>
       <c r="J88" t="inlineStr">
@@ -5242,7 +5254,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5257,12 +5269,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB002679</t>
+          <t>MB002695</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml</t>
+          <t>Niacinamide 10 TXA 4 Serum: sérum para manchas e luminosidade 30 ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5271,7 +5283,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>217.9</v>
+        <v>174.9</v>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
@@ -5280,12 +5292,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
+          <t>Niacinamide 10 TXA 4 Serum for Brightening and Dark Spots</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I89" s="4" t="n"/>
       <c r="J89" t="inlineStr">
@@ -5295,7 +5307,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
+          <t>https://anua.us/products/niacinamide-10-txa-4-serum-copy-1</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -5310,12 +5322,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003838</t>
+          <t>MB003848</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
+          <t>Niacinamide TXA Brightening Booster Toner: tônico iluminador 250 ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5324,7 +5336,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>582.9</v>
+        <v>152.9</v>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
@@ -5333,16 +5345,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Peach Brightening Set</t>
+          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I90" s="4" t="n"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5350,7 +5360,7 @@
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-brightening-set</t>
+          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
         </is>
       </c>
       <c r="L90" s="2">
@@ -5365,12 +5375,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MB002665</t>
+          <t>MB002679</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Redness Soothing Duo: tônico Azelaic 3 Cica + sérum de ácido azelaico 10%</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5379,7 +5389,7 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>327.9</v>
+        <v>217.9</v>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
@@ -5388,16 +5398,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Redness Soothing Duo</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>49</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I91" s="4" t="n"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/redness-soothing-duo</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
         </is>
       </c>
       <c r="L91" s="2">
@@ -5420,12 +5428,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MB003856</t>
+          <t>MB003838</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
+          <t>Peach Brightening Set: rotina iluminadora de pêssego e niacinamida em 4 passos</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5434,7 +5442,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>305.9</v>
+        <v>582.9</v>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
@@ -5443,15 +5451,15 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skin Recovery Duo</t>
+          <t>Peach Brightening Set</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" s="4" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5460,7 +5468,7 @@
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/skin-recovery-duo</t>
+          <t>https://anua.us/products/peach-brightening-set</t>
         </is>
       </c>
       <c r="L92" s="2">
@@ -5475,12 +5483,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MB002652</t>
+          <t>MB002665</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Spotless Skin Duo: sérum de niacinamida + TXA e sérum de ácido azelaico</t>
+          <t>Redness Soothing Duo: tônico Azelaic 3 Cica + sérum de ácido azelaico 10%</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5489,7 +5497,7 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>319.9</v>
+        <v>327.9</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -5498,15 +5506,15 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spotless Skin Duo</t>
+          <t>Redness Soothing Duo</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" s="4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5515,7 +5523,7 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/ultimate-spot-duo</t>
+          <t>https://anua.us/products/redness-soothing-duo</t>
         </is>
       </c>
       <c r="L93" s="2">
@@ -5530,21 +5538,21 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MB003842</t>
+          <t>MB003856</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
+          <t>Skin Recovery Duo: sérum de ácido azelaico 10% + creme de 3 ceramidas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>108.9</v>
+        <v>305.9</v>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
@@ -5553,14 +5561,16 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+          <t>Skin Recovery Duo</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I94" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>50</v>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5568,7 +5578,7 @@
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+          <t>https://anua.us/products/skin-recovery-duo</t>
         </is>
       </c>
       <c r="L94" s="2">
@@ -5583,21 +5593,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MB003875</t>
+          <t>MB002652</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
+          <t>Spotless Skin Duo: sérum de niacinamida + TXA e sérum de ácido azelaico</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>144.9</v>
+        <v>319.9</v>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
@@ -5606,14 +5616,16 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
+          <t>Spotless Skin Duo</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I95" s="4" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>56</v>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5621,7 +5633,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
+          <t>https://anua.us/products/ultimate-spot-duo</t>
         </is>
       </c>
       <c r="L95" s="2">
@@ -5636,12 +5648,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MB003868</t>
+          <t>MB002710</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
+          <t>Heartleaf 70% Creme Calmante Intenso</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5650,7 +5662,7 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1821.9</v>
+        <v>188.9</v>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
@@ -5659,16 +5671,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
+          <t>Heartleaf 70% Intense Calming Cream</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>333.8</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I96" s="4" t="n"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5676,7 +5686,7 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/heartleaf-70-intense-calming-cream</t>
         </is>
       </c>
       <c r="L96" s="2">
@@ -5691,12 +5701,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MB002689</t>
+          <t>MB003842</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sérum Facial em Spray PDRN Collagen Glow</t>
+          <t>Hydrating Cleansing Foam with Hyaluronic Acid PDRN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5705,7 +5715,7 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>210.9</v>
+        <v>108.9</v>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
@@ -5714,12 +5724,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PDRN Collagen Glow Facial Serum Spray</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I97" s="4" t="n"/>
       <c r="J97" t="inlineStr">
@@ -5729,7 +5739,7 @@
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-hydrating-capsule-mist-100ml-1</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L97" s="2">
@@ -5744,12 +5754,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MB002672</t>
+          <t>MB002712</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sérum Peach 70% Niacinamida</t>
+          <t>Loção Diária Heartleaf 70</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5758,7 +5768,7 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>159.9</v>
+        <v>188.9</v>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
@@ -5767,12 +5777,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Peach 70% Niacinamide Serum</t>
+          <t>Heartleaf 70 Daily Lotion</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I98" s="4" t="n"/>
       <c r="J98" t="inlineStr">
@@ -5782,7 +5792,7 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
+          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
         </is>
       </c>
       <c r="L98" s="2">
@@ -5797,35 +5807,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MB003843</t>
+          <t>MB003875</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Golden Honmoon Ceramide Barrier Collagen Mask: máscara de colágeno (4 un.)</t>
+          <t>Mini Spray Sérum Facial PDRN Colágeno Glow</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>144.9</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+          <t>PDRN Collagen Glow Facial Serum Spray Mini</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I99" s="4" t="n"/>
       <c r="J99" t="inlineStr">
@@ -5835,7 +5845,7 @@
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+          <t>https://anua.us/products/pdrn-collagen-glow-facial-serum-spray-mini</t>
         </is>
       </c>
       <c r="L99" s="2">
@@ -5850,30 +5860,30 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MB002711</t>
+          <t>MB002661</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Soothing Collagen Mask: máscara calmante de colágeno (4 unidades)</t>
+          <t>Máscara de Colágeno Rice 70 Glow</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
         <v>159.9</v>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Soothing Collagen Mask</t>
+          <t>Rice 70 Glow Collagen Mask</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5888,7 +5898,7 @@
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-soothing-collagen-mask</t>
+          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
         </is>
       </c>
       <c r="L100" s="2">
@@ -5903,37 +5913,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MB002687</t>
+          <t>MB003868</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Glass Skin: adesivo de colágeno para o rosto (4 un.)</t>
+          <t>PDRN Glow Boost: Kit Completo de Rotina</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>1821.9</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Glass Skin 4ea</t>
+          <t>PDRN Glow Boost Full Routine Set</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I101" s="4" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>333.8</v>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5941,7 +5953,7 @@
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-glass-skin-4ea-1</t>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
         </is>
       </c>
       <c r="L101" s="2">
@@ -5956,35 +5968,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MB003844</t>
+          <t>MB002672</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Neck: adesivo de colágeno para o pescoço (4 un.)</t>
+          <t>Sérum Peach 70% Niacinamida</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>159.9</v>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PDRN Collagen Melting Patch For Neck 4ea</t>
+          <t>Peach 70% Niacinamide Serum</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I102" s="4" t="n"/>
       <c r="J102" t="inlineStr">
@@ -5994,7 +6006,7 @@
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-neck-4ea-1</t>
+          <t>https://anua.us/products/peach-70-niacinamide-serum-copy</t>
         </is>
       </c>
       <c r="L102" s="2">
@@ -6009,35 +6021,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MB003825</t>
+          <t>MB002660</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Peach 70 Niacin Brightening Collagen Mask: máscara iluminadora de colágeno (4 un.)</t>
+          <t>Tônico Leitoso Rice 70 Glow</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>166.9</v>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Peach 70 Niacin Brightening Collagen Mask</t>
+          <t>Rice 70 Glow Milky Toner</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I103" s="4" t="n"/>
       <c r="J103" t="inlineStr">
@@ -6047,7 +6059,7 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-70-niacin-brightening-collagen-mask-1</t>
+          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
         </is>
       </c>
       <c r="L103" s="2">
@@ -6062,12 +6074,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MB003827</t>
+          <t>MB003843</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Collagen Mask: máscara de colágeno com arroz (4 unidades)</t>
+          <t>Golden Honmoon Ceramide Barrier Collagen Mask: máscara de colágeno (4 un.)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6076,7 +6088,7 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>159.9</v>
+        <v>152.9</v>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
@@ -6085,12 +6097,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Collagen Mask</t>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I104" s="4" t="n"/>
       <c r="J104" t="inlineStr">
@@ -6100,7 +6112,7 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
         </is>
       </c>
       <c r="L104" s="2">
@@ -6115,21 +6127,21 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MB002713</t>
+          <t>MB002711</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
+          <t>Heartleaf 70 Soothing Collagen Mask: máscara calmante de colágeno (4 unidades)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>152.9</v>
+        <v>159.9</v>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
@@ -6138,12 +6150,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+          <t>Heartleaf 70 Soothing Collagen Mask</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I105" s="4" t="n"/>
       <c r="J105" t="inlineStr">
@@ -6153,7 +6165,7 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+          <t>https://anua.us/products/heartleaf-70-soothing-collagen-mask</t>
         </is>
       </c>
       <c r="L105" s="2">
@@ -6168,21 +6180,21 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MB003863</t>
+          <t>MB002687</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
+          <t>PDRN Collagen Melting Patch For Glass Skin: adesivo de colágeno para o rosto (4 un.)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>152.9</v>
+        <v>144.9</v>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
@@ -6191,12 +6203,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
+          <t>PDRN Collagen Melting Patch For Glass Skin 4ea</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I106" s="4" t="n"/>
       <c r="J106" t="inlineStr">
@@ -6206,7 +6218,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
+          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-glass-skin-4ea-1</t>
         </is>
       </c>
       <c r="L106" s="2">
@@ -6221,21 +6233,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MB004044</t>
+          <t>MB003844</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml (kit com 2)</t>
+          <t>PDRN Collagen Melting Patch For Neck: adesivo de colágeno para o pescoço (4 un.)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>437.9</v>
+        <v>144.9</v>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
@@ -6244,12 +6256,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
+          <t>PDRN Collagen Melting Patch For Neck 4ea</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I107" s="4" t="n"/>
       <c r="J107" t="inlineStr">
@@ -6259,7 +6271,7 @@
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
+          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-neck-4ea-1</t>
         </is>
       </c>
       <c r="L107" s="2">
@@ -6274,12 +6286,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MB003855</t>
+          <t>MB003825</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7-Day Ultimate Glass Glow Set: rotina glass skin em 7 passos</t>
+          <t>Peach 70 Niacin Brightening Collagen Mask: máscara iluminadora de colágeno (4 un.)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6288,25 +6300,23 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>844.9</v>
+        <v>159.9</v>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>7-Day Glass Skin Set</t>
+          <t>Peach 70 Niacin Brightening Collagen Mask</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="I108" s="4" t="n">
-        <v>165</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I108" s="4" t="n"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6314,7 +6324,7 @@
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/7-day-glass-skin-set</t>
+          <t>https://anua.us/products/peach-70-niacin-brightening-collagen-mask-1</t>
         </is>
       </c>
       <c r="L108" s="2">
@@ -6329,12 +6339,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MB002729</t>
+          <t>MB003827</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Azelaic 10 &amp; Hyaluronic Redness Calming Disk</t>
+          <t>Rice 70 Glow Collagen Mask: máscara de colágeno com arroz (4 unidades)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6343,21 +6353,21 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>167.9</v>
+        <v>159.9</v>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Azelaic 10 Hyaluron Redness Soothing Pad</t>
+          <t>Rice 70 Glow Collagen Mask</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I109" s="4" t="n"/>
       <c r="J109" t="inlineStr">
@@ -6367,7 +6377,7 @@
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/azelaic-10-hyaluron-redness-soothing-pad</t>
+          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
         </is>
       </c>
       <c r="L109" s="2">
@@ -6382,35 +6392,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MB002720</t>
+          <t>MB002686</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Creme Gua Sha Refinador de Colágeno e Retinol</t>
+          <t>Adesivo de Colágeno PDRN para o Pescoço (4 unidades)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>254.9</v>
+        <v>145.9</v>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Collagen Retinol Refining Gua Sha Cream</t>
+          <t>PDRN Collagen Melting Patch For Glass Skin 4ea</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I110" s="4" t="n"/>
       <c r="J110" t="inlineStr">
@@ -6420,7 +6430,7 @@
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
+          <t>https://anua.us/products/pdrn-collagen-melting-patch-for-glass-skin-4ea-1</t>
         </is>
       </c>
       <c r="L110" s="2">
@@ -6435,35 +6445,35 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MB002691</t>
+          <t>MB002713</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Disco Glow PDRN 100 e Ácido Hialurônico</t>
+          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>166.9</v>
+        <v>152.9</v>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I111" s="4" t="n"/>
       <c r="J111" t="inlineStr">
@@ -6473,7 +6483,7 @@
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
         </is>
       </c>
       <c r="L111" s="2">
@@ -6488,35 +6498,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MB003817</t>
+          <t>MB003863</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Heartleaf Low pH Deep Cleansing Water: água de limpeza de pH baixo</t>
+          <t>Máscara de Colágeno Golden Honmoon Barrier (4 unidades)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>159.9</v>
+        <v>152.9</v>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
+          <t>Golden Honmoon Barrier Collagen Mask 4ea</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I112" s="4" t="n"/>
       <c r="J112" t="inlineStr">
@@ -6526,7 +6536,7 @@
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
+          <t>https://anua.us/products/golden-honmoon-barrier-collagen-mask-4ea</t>
         </is>
       </c>
       <c r="L112" s="2">
@@ -6541,35 +6551,35 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MB002692</t>
+          <t>MB004044</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PDRN 100 Tônico Booster e Ácido Hialurônico</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum: sérum de PDRN com cápsulas 30 ml (kit com 2)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>152.9</v>
+        <v>437.9</v>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>PDRN Hyaluronic Acid Capsule 100 Serum</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I113" s="4" t="n"/>
       <c r="J113" t="inlineStr">
@@ -6579,7 +6589,7 @@
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-capsule-100-serum-1</t>
         </is>
       </c>
       <c r="L113" s="2">
@@ -6594,12 +6604,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MB002696</t>
+          <t>MB003855</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sérum Renovador Nano Retinol™ 0,3% + Niacina</t>
+          <t>7-Day Ultimate Glass Glow Set: rotina glass skin em 7 passos</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6608,7 +6618,7 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>181.9</v>
+        <v>844.9</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
@@ -6617,14 +6627,16 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
+          <t>7-Day Glass Skin Set</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I114" s="4" t="n"/>
+        <v>116</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>165</v>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6632,7 +6644,7 @@
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
+          <t>https://anua.us/products/7-day-glass-skin-set</t>
         </is>
       </c>
       <c r="L114" s="2">
@@ -6647,21 +6659,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MB003870</t>
+          <t>MB002729</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Duo Essencial Diário PDRN</t>
+          <t>Azelaic 10 &amp; Hyaluronic Redness Calming Disk</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>46</v>
+        <v>167.9</v>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
@@ -6670,16 +6682,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
+          <t>Azelaic 10 Hyaluron Redness Soothing Pad</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="I115" s="4" t="n">
-        <v>51</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I115" s="4" t="n"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6687,7 +6697,7 @@
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
+          <t>https://anua.us/products/azelaic-10-hyaluron-redness-soothing-pad</t>
         </is>
       </c>
       <c r="L115" s="2">
@@ -6702,21 +6712,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MB002653</t>
+          <t>MB002720</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Duo de Recuperação para a Pele</t>
+          <t>Creme Gua Sha Refinador de Colágeno e Retinol</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>306.9</v>
+        <v>254.9</v>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
@@ -6725,16 +6735,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Double Cleansing Duo Set of 2</t>
+          <t>Collagen Retinol Refining Gua Sha Cream</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="I116" s="4" t="n">
-        <v>114</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I116" s="4" t="n"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6742,7 +6750,7 @@
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
+          <t>https://anua.us/products/collagen-retinol-refining-gua-sha-cream-1</t>
         </is>
       </c>
       <c r="L116" s="2">
@@ -6757,21 +6765,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MB002704</t>
+          <t>MB002691</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Hydrating Exfoliant Gel</t>
+          <t>Disco Glow PDRN 100 e Ácido Hialurônico</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>159.9</v>
+        <v>166.9</v>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
@@ -6780,12 +6788,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Heartleaf LHA Moisture Peeling Gel</t>
+          <t>PDRN 100 Hyaluronic Acid Glow Pad</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I117" s="4" t="n"/>
       <c r="J117" t="inlineStr">
@@ -6795,7 +6803,7 @@
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-glow-pad-1</t>
         </is>
       </c>
       <c r="L117" s="2">
@@ -6810,21 +6818,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MB002731</t>
+          <t>MB003817</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hidrating Gentle Cleanser with 8 Hyaluronic Acids</t>
+          <t>Heartleaf Low pH Deep Cleansing Water: água de limpeza de pH baixo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>109.9</v>
+        <v>159.9</v>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
@@ -6833,12 +6841,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>8 Hyaluronic Acid Moisturizing Gentle Gel Cleanser</t>
+          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I118" s="4" t="n"/>
       <c r="J118" t="inlineStr">
@@ -6848,7 +6856,7 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/8-hyaluronic-acid-moisturizing-gentle-gel-cleanser</t>
+          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
         </is>
       </c>
       <c r="L118" s="2">
@@ -6863,21 +6871,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MB002668</t>
+          <t>MB002692</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kit Iluminador Peach</t>
+          <t>PDRN 100 Tônico Booster e Ácido Hialurônico</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>582.9</v>
+        <v>152.9</v>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
@@ -6886,16 +6894,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Peach Brightening Set</t>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I119" s="4" t="n"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6903,7 +6909,7 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/peach-brightening-set</t>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
         </is>
       </c>
       <c r="L119" s="2">
@@ -6918,21 +6924,21 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MB002682</t>
+          <t>MB002696</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kit Rotina Completa PDRN Glow Boost</t>
+          <t>Sérum Renovador Nano Retinol™ 0,3% + Niacina</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1821.9</v>
+        <v>181.9</v>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
@@ -6941,16 +6947,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PDRN Glow Boost Full Routine Set</t>
+          <t>Nano Retinol 0.3% + Niacin Renewing Serum</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I120" s="4" t="n">
-        <v>333.8</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I120" s="4" t="n"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -6958,7 +6962,7 @@
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+          <t>https://anua.us/products/nano-retinol-0-3-niacin-renewing-serum-1</t>
         </is>
       </c>
       <c r="L120" s="2">
@@ -6973,12 +6977,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MB002712</t>
+          <t>MB003870</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Loção Diária Heartleaf 70</t>
+          <t>Duo Essencial Diário PDRN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6987,7 +6991,7 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>188.9</v>
+        <v>46</v>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
@@ -6996,14 +7000,16 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Heartleaf 70 Daily Lotion</t>
+          <t>PDRN Deep Hydrating Prep &amp; Boost Duo</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I121" s="4" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -7011,7 +7017,7 @@
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/heartleaf-70-daily-lotion-copy-1</t>
+          <t>https://anua.us/products/pdrn-deep-hydrating-prep-boost-duo</t>
         </is>
       </c>
       <c r="L121" s="2">
@@ -7026,12 +7032,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MB002661</t>
+          <t>MB002653</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Rice 70 Glow</t>
+          <t>Duo de Recuperação para a Pele</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7040,7 +7046,7 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>159.9</v>
+        <v>306.9</v>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
@@ -7049,14 +7055,16 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Collagen Mask</t>
+          <t>Double Cleansing Duo Set of 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I122" s="4" t="n"/>
+        <v>78</v>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>114</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -7064,7 +7072,7 @@
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-collagen-mask-1</t>
+          <t>https://anua.us/products/holiday-exclusive-bogo-double-cleansing-duo-free-gifts</t>
         </is>
       </c>
       <c r="L122" s="2">
@@ -7079,12 +7087,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MB002676</t>
+          <t>MB003812</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sérum Labial PDRN</t>
+          <t>Espuma de Limpeza Profunda para Poros com Heartleaf e Quercetinol</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7093,7 +7101,7 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
@@ -7102,12 +7110,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PDRN Lip Serum</t>
+          <t>Heartleaf Quercetinol Pore Deep Cleansing Foam</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I123" s="4" t="n"/>
       <c r="J123" t="inlineStr">
@@ -7117,7 +7125,7 @@
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-lip-serum</t>
+          <t>https://anua.us/products/heartleaf-quercetinol-pore-deep-cleansing-foam-1</t>
         </is>
       </c>
       <c r="L123" s="2">
@@ -7132,12 +7140,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MB003841</t>
+          <t>MB002732</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tônico Booster PDRN 100 com Ácido Hialurônico</t>
+          <t>Espuma de Limpeza Suave Hidratante com 8 Ácidos Hialurônicos</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7146,7 +7154,7 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>152.9</v>
+        <v>999.99</v>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
@@ -7155,12 +7163,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I124" s="4" t="n"/>
       <c r="J124" t="inlineStr">
@@ -7170,7 +7178,7 @@
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
         </is>
       </c>
       <c r="L124" s="2">
@@ -7185,12 +7193,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MB002660</t>
+          <t>MB002704</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tônico Leitoso Rice 70 Glow</t>
+          <t>Heartleaf LHA Hydrating Exfoliant Gel</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7199,7 +7207,7 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>166.9</v>
+        <v>159.9</v>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
@@ -7208,12 +7216,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rice 70 Glow Milky Toner</t>
+          <t>Heartleaf LHA Moisture Peeling Gel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I125" s="4" t="n"/>
       <c r="J125" t="inlineStr">
@@ -7223,7 +7231,7 @@
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>https://anua.us/products/rice-70-glow-milky-toner-copy</t>
+          <t>https://anua.us/products/heartleaf-lha-moisture-peeling-gel-copy</t>
         </is>
       </c>
       <c r="L125" s="2">
@@ -7238,12 +7246,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MB003857</t>
+          <t>MB002731</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Adesivo Derretível de Colágeno PDRN para Pescoço (4 unidades)</t>
+          <t>Hidrating Gentle Cleanser with 8 Hyaluronic Acids</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7252,27 +7260,51 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="n"/>
+        <v>109.9</v>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>8 Hyaluronic Acid Moisturizing Gentle Gel Cleanser</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I126" s="4" t="n"/>
-      <c r="L126" s="2" t="n"/>
-      <c r="M126" s="6" t="n"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/8-hyaluronic-acid-moisturizing-gentle-gel-cleanser</t>
+        </is>
+      </c>
+      <c r="L126" s="2">
+        <f>ROUND(H126*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M126" s="6">
+        <f>IF(OR(D126="",L126=""),"",D126/L126-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MB002650</t>
+          <t>MB002668</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Adesivo Ultrafino para Acne</t>
+          <t>Kit Iluminador Peach</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7281,27 +7313,53 @@
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="n"/>
-      <c r="I127" s="4" t="n"/>
-      <c r="L127" s="2" t="n"/>
-      <c r="M127" s="6" t="n"/>
+        <v>582.9</v>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Peach Brightening Set</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I127" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-brightening-set</t>
+        </is>
+      </c>
+      <c r="L127" s="2">
+        <f>ROUND(H127*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M127" s="6">
+        <f>IF(OR(D127="",L127=""),"",D127/L127-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MB002686</t>
+          <t>MB002682</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Adesivo de Colágeno PDRN para o Pescoço (4 unidades)</t>
+          <t>Kit Rotina Completa PDRN Glow Boost</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7310,27 +7368,53 @@
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="n"/>
-      <c r="I128" s="4" t="n"/>
-      <c r="L128" s="2" t="n"/>
-      <c r="M128" s="6" t="n"/>
+        <v>1821.9</v>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>PDRN Glow Boost Full Routine Set</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I128" s="4" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-glow-boost-full-routine-set</t>
+        </is>
+      </c>
+      <c r="L128" s="2">
+        <f>ROUND(H128*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M128" s="6">
+        <f>IF(OR(D128="",L128=""),"",D128/L128-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MB003994</t>
+          <t>MB002659</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Anua Kit de Patches Firmadores Melting com Colágeno PDRN</t>
+          <t>Loção Hidratante Intensiva Rice 70</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7339,27 +7423,51 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Rice 70 Intensive Moisturizing Milk</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I129" s="4" t="n"/>
-      <c r="L129" s="2" t="n"/>
-      <c r="M129" s="6" t="n"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/rice-70-intensive-moisturizing-milk</t>
+        </is>
+      </c>
+      <c r="L129" s="2">
+        <f>ROUND(H129*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M129" s="6">
+        <f>IF(OR(D129="",L129=""),"",D129/L129-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MB002699</t>
+          <t>MB002673</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bastão Solar com Acabamento Glow Invisível</t>
+          <t>Máscara Iluminadora de Colágeno Peach 70 e Niacina</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7368,27 +7476,51 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Peach 70 Niacin Brightening Collagen Mask</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" s="4" t="n">
+        <v>22</v>
+      </c>
       <c r="I130" s="4" t="n"/>
-      <c r="L130" s="2" t="n"/>
-      <c r="M130" s="6" t="n"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-70-niacin-brightening-collagen-mask-1</t>
+        </is>
+      </c>
+      <c r="L130" s="2">
+        <f>ROUND(H130*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M130" s="6">
+        <f>IF(OR(D130="",L130=""),"",D130/L130-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MB002733</t>
+          <t>MB002693</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Calming Pad 8 Tipos de Ácido Hialurônico e Catequina</t>
+          <t>Niacinamide e Ácido Tranexâmico Tônico Booster Iluminador</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7397,27 +7529,51 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Niacinamide Tranexamic Acid Brightening Booster Toner</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="I131" s="4" t="n"/>
-      <c r="L131" s="2" t="n"/>
-      <c r="M131" s="6" t="n"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/niacinamide-tranexamic-acid-brightening-booster-toner-1</t>
+        </is>
+      </c>
+      <c r="L131" s="2">
+        <f>ROUND(H131*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M131" s="6">
+        <f>IF(OR(D131="",L131=""),"",D131/L131-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MB002738</t>
+          <t>MB002677</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Creme Barreira com 3 Ceramidas e Pantenol</t>
+          <t>PDRN e Ácido Hialurônico Espuma de Limpeza Hidratante</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7426,27 +7582,51 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="n"/>
+        <v>108.9</v>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>PDRN Hyaluronic Acid Moisturizing Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I132" s="4" t="n"/>
-      <c r="L132" s="2" t="n"/>
-      <c r="M132" s="6" t="n"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-hyaluronic-acid-moisturizing-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L132" s="2">
+        <f>ROUND(H132*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M132" s="6">
+        <f>IF(OR(D132="",L132=""),"",D132/L132-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MB002670</t>
+          <t>MB002657</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Creme Enriquecido de Pêssego 77 Niacinamida</t>
+          <t>Pó de Limpeza Iluminador de Enzima de Arroz</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7455,27 +7635,51 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Rice Enzyme Brightening Cleansing Powder</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I133" s="4" t="n"/>
-      <c r="L133" s="2" t="n"/>
-      <c r="M133" s="6" t="n"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/rice-enzyme-brightening-cleansing-powder-1</t>
+        </is>
+      </c>
+      <c r="L133" s="2">
+        <f>ROUND(H133*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M133" s="6">
+        <f>IF(OR(D133="",L133=""),"",D133/L133-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MB002694</t>
+          <t>MB003841</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Disco Iluminador Niacinamida 5 e TXA</t>
+          <t>Tônico Booster PDRN 100 com Ácido Hialurônico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7484,27 +7688,51 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>PDRN 100 Hyaluronic Acid Booster Toner</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="I134" s="4" t="n"/>
-      <c r="L134" s="2" t="n"/>
-      <c r="M134" s="6" t="n"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/pdrn-100-hyaluronic-acid-booster-toner-1</t>
+        </is>
+      </c>
+      <c r="L134" s="2">
+        <f>ROUND(H134*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M134" s="6">
+        <f>IF(OR(D134="",L134=""),"",D134/L134-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MB002721</t>
+          <t>MB002728</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Duo de Cuidado para Acne</t>
+          <t>Tônico Clareador Azelaico 3 Cica</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7513,27 +7741,51 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="n"/>
+        <v>153.9</v>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Azelaic 3 Cica Skin Clarifying Toner</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="I135" s="4" t="n"/>
-      <c r="L135" s="2" t="n"/>
-      <c r="M135" s="6" t="n"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/azelaic-3-cica-skin-clarifying-toner</t>
+        </is>
+      </c>
+      <c r="L135" s="2">
+        <f>ROUND(H135*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M135" s="6">
+        <f>IF(OR(D135="",L135=""),"",D135/L135-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MB003812</t>
+          <t>MB002722</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Espuma de Limpeza Profunda para Poros com Heartleaf e Quercetinol</t>
+          <t>Tônico Esfoliante BHA 2%</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7542,27 +7794,51 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="n"/>
+        <v>145.9</v>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>BHA 2% Gentle Exfoliating Toner</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I136" s="4" t="n"/>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="6" t="n"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/bha-2-gentle-exfoliating-toner</t>
+        </is>
+      </c>
+      <c r="L136" s="2">
+        <f>ROUND(H136*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M136" s="6">
+        <f>IF(OR(D136="",L136=""),"",D136/L136-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MB002732</t>
+          <t>MB003845</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Espuma de Limpeza Suave Hidratante com 8 Ácidos Hialurônicos</t>
+          <t>Tônico Essência de Pêssego 77 com Niacinamida</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7571,27 +7847,51 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="n"/>
+        <v>181.9</v>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Peach 77 Niacin Essence Toner</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="I137" s="4" t="n"/>
-      <c r="L137" s="2" t="n"/>
-      <c r="M137" s="6" t="n"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/peach-77-niacin-essence-toner-1</t>
+        </is>
+      </c>
+      <c r="L137" s="2">
+        <f>ROUND(H137*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M137" s="6">
+        <f>IF(OR(D137="",L137=""),"",D137/L137-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MB002710</t>
+          <t>MB002702</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Heartleaf 70% Creme Calmante Intenso</t>
+          <t>Óleo de Limpeza Suave de Poros Heartleaf</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7600,27 +7900,51 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Heartleaf Pore Control Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" s="4" t="n">
+        <v>22</v>
+      </c>
       <c r="I138" s="4" t="n"/>
-      <c r="L138" s="2" t="n"/>
-      <c r="M138" s="6" t="n"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>https://anua.us/products/heartleaf-pore-control-cleansing-oil-200ml</t>
+        </is>
+      </c>
+      <c r="L138" s="2">
+        <f>ROUND(H138*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M138" s="6">
+        <f>IF(OR(D138="",L138=""),"",D138/L138-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MB003839</t>
+          <t>MB003857</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Kit Completo Nutritivo de Arroz para Pele Seca</t>
+          <t>Adesivo Derretível de Colágeno PDRN para Pescoço (4 unidades)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7629,7 +7953,7 @@
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>680.9</v>
+        <v>145.9</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -7644,12 +7968,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MB002690</t>
+          <t>MB002650</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kit PDRN 4 Passos Pele Luminosa</t>
+          <t>Adesivo Ultrafino para Acne</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7658,7 +7982,7 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>874.9</v>
+        <v>999.99</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -7673,12 +7997,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MB003860</t>
+          <t>MB003994</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kit PDRN Glowy Skin 4 Passos</t>
+          <t>Anua Kit de Patches Firmadores Melting com Colágeno PDRN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7687,7 +8011,7 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>874.9</v>
+        <v>145.9</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -7702,12 +8026,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MB003873</t>
+          <t>MB002699</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kit PDRN Luminosidade Radiante o Dia Todo</t>
+          <t>Bastão Solar com Acabamento Glow Invisível</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7716,7 +8040,7 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>95</v>
+        <v>999.99</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -7731,12 +8055,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MB002735</t>
+          <t>MB002733</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kit Rotina 7 Dias Manchas Escuras</t>
+          <t>Calming Pad 8 Tipos de Ácido Hialurônico e Catequina</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7745,7 +8069,7 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1012.9</v>
+        <v>167.9</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -7760,12 +8084,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MB002730</t>
+          <t>MB002738</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Kit Rotina Antienvelhecimento</t>
+          <t>Creme Barreira com 3 Ceramidas e Pantenol</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7774,7 +8098,7 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>838.9</v>
+        <v>999.99</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -7789,12 +8113,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MB002734</t>
+          <t>MB002670</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Kit Rotina Refino de Poros 7 Dias</t>
+          <t>Creme Enriquecido de Pêssego 77 Niacinamida</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7803,7 +8127,7 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1013.9</v>
+        <v>189.9</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -7818,12 +8142,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MB002736</t>
+          <t>MB002694</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Kit Rotina de 7 Dias para Controle da Acne</t>
+          <t>Disco Iluminador Niacinamida 5 e TXA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7832,7 +8156,7 @@
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>999.99</v>
+        <v>166.9</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -7847,12 +8171,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MB003866</t>
+          <t>MB002721</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Leite Condicionador de Pêssego 77 Niacina</t>
+          <t>Duo de Cuidado para Acne</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7861,7 +8185,7 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>181.9</v>
+        <v>999.99</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -7876,12 +8200,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MB002659</t>
+          <t>MB003839</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Loção Hidratante Intensiva Rice 70</t>
+          <t>Kit Completo Nutritivo de Arroz para Pele Seca</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7890,7 +8214,7 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>144.9</v>
+        <v>680.9</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -7905,12 +8229,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MB002671</t>
+          <t>MB002690</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Loção Leitosa de Niacina Peach 77</t>
+          <t>Kit PDRN 4 Passos Pele Luminosa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7919,7 +8243,7 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>999.99</v>
+        <v>874.9</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7934,12 +8258,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MB002673</t>
+          <t>MB003860</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Máscara Iluminadora de Colágeno Peach 70 e Niacina</t>
+          <t>Kit PDRN Glowy Skin 4 Passos</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7948,7 +8272,7 @@
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>160.9</v>
+        <v>874.9</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7963,12 +8287,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MB003826</t>
+          <t>MB003873</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Máscara de Colágeno Calmante com Houttuynia Cordata 70</t>
+          <t>Kit PDRN Luminosidade Radiante o Dia Todo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7977,7 +8301,7 @@
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>159.9</v>
+        <v>95</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7992,12 +8316,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MB002693</t>
+          <t>MB002735</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Niacinamide e Ácido Tranexâmico Tônico Booster Iluminador</t>
+          <t>Kit Rotina 7 Dias Manchas Escuras</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8006,7 +8330,7 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>152.9</v>
+        <v>1012.9</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -8021,12 +8345,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MB002677</t>
+          <t>MB002730</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PDRN e Ácido Hialurônico Espuma de Limpeza Hidratante</t>
+          <t>Kit Rotina Antienvelhecimento</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8035,7 +8359,7 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>108.9</v>
+        <v>838.9</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -8050,12 +8374,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MB003830</t>
+          <t>MB002734</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Patch Microagulhado para Tratamento de Espinhas com Tríplice Ácido</t>
+          <t>Kit Rotina Refino de Poros 7 Dias</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8064,7 +8388,7 @@
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>108.9</v>
+        <v>1013.9</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -8079,12 +8403,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MB002657</t>
+          <t>MB002736</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Pó de Limpeza Iluminador de Enzima de Arroz</t>
+          <t>Kit Rotina de 7 Dias para Controle da Acne</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8093,7 +8417,7 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>144.9</v>
+        <v>999.99</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -8108,12 +8432,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MB002658</t>
+          <t>MB003866</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sérum Hidratante Fortalecedor da Barreira de Pele com Ceramidas de Arroz 7</t>
+          <t>Leite Condicionador de Pêssego 77 Niacina</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8122,7 +8446,7 @@
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>166.9</v>
+        <v>181.9</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -8137,12 +8461,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MB003840</t>
+          <t>MB002671</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sérum PDRN Cápsula 100 de Ácido Hialurônico – Dose Única</t>
+          <t>Loção Leitosa de Niacina Peach 77</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8151,7 +8475,7 @@
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>181.9</v>
+        <v>999.99</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -8166,12 +8490,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MB003867</t>
+          <t>MB003826</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tônico Booster Iluminador com Niacinamida e Ácido Tranexâmico</t>
+          <t>Máscara de Colágeno Calmante com Houttuynia Cordata 70</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8180,7 +8504,7 @@
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>152.9</v>
+        <v>159.9</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -8195,12 +8519,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MB002728</t>
+          <t>MB003830</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tônico Clareador Azelaico 3 Cica</t>
+          <t>Patch Microagulhado para Tratamento de Espinhas com Tríplice Ácido</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8209,7 +8533,7 @@
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>153.9</v>
+        <v>108.9</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -8224,12 +8548,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MB002722</t>
+          <t>MB002658</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tônico Esfoliante BHA 2%</t>
+          <t>Sérum Hidratante Fortalecedor da Barreira de Pele com Ceramidas de Arroz 7</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8238,7 +8562,7 @@
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>145.9</v>
+        <v>166.9</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -8253,12 +8577,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MB003845</t>
+          <t>MB003840</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tônico Essência de Pêssego 77 com Niacinamida</t>
+          <t>Sérum PDRN Cápsula 100 de Ácido Hialurônico – Dose Única</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8282,12 +8606,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MB002703</t>
+          <t>MB003867</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Água de Limpeza Profunda Low pH Heartleaf</t>
+          <t>Tônico Booster Iluminador com Niacinamida e Ácido Tranexâmico</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8296,7 +8620,7 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>159.9</v>
+        <v>152.9</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -8311,12 +8635,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MB002702</t>
+          <t>MB002703</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Óleo de Limpeza Suave de Poros Heartleaf</t>
+          <t>Água de Limpeza Profunda Low pH Heartleaf</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8325,7 +8649,7 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>144.9</v>
+        <v>159.9</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -8463,10 +8787,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12575,7 +12912,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://anua.us · loja "Anua US" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
